--- a/data/image_processing_data.xlsx
+++ b/data/image_processing_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project -V2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32281483-1DD9-46A1-8EF9-8668F918C64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B463E6A-211E-450E-AC67-601169A59734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F1D4E91A-2F46-4F25-B10D-F24B53DDC6F9}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="777">
   <si>
     <t>Title</t>
   </si>
@@ -1468,6 +1468,919 @@
   </si>
   <si>
     <t>Ziwen Ke</t>
+  </si>
+  <si>
+    <t>Quality Identification and Grading of Wheat Grains using Image Processing Techniques</t>
+  </si>
+  <si>
+    <t>Food is the basic need which provides nutrients to our body. Quality of food is the most necessary thing to be checked as the adulteration of food grains is increasing on a greater pace. Existing quality assessment is done manually which is tedious and include human errors (unknowingly or intentionally). This will affect the farmer who is relying on the farm for his daily bread, they don’t get fair price after their years together efforts in farm. Manual Assessment is also encouraging adulteration of food grains thus deceiving the customers by mixing bad quality grains or materials which resemble the grains and gaining high margin profit. Automation is utmost necessary when human inspection is misleading the society and selling cheap quality food. This project illustrates the automatic grading system which process the grain image digitally and classify the grains into Good, Average and Bad class by taking predefined values into consideration with the help of Digital Image Processing and the grains, weed particles, stones and other foreign materials are easily distinguished. This can be achieved by training the system with a set of images and using these results, the system will test the input image. It can automate the process which is reliable, factual and time saving.</t>
+  </si>
+  <si>
+    <t>Image Processing in Polarimetric SAR Images Using a Hybrid Entropy Decomposition and Maximum Likelihood (EDML)</t>
+  </si>
+  <si>
+    <t>This paper presents a hybrid entropy decomposition and maximum likelihood (EDML) for synthetic aperture radar (SAR) image analysis and classification with the application of land use management. Entropy decomposition is an effective technique to obtain valuable decomposed parameters for image interpretation with analysis of the underlying scattering mechanisms. However, the main disadvantage of entropy decomposition is that the decision boundaries of the analysis plane are arbitrary. To overcome this problem, maximum likelihood technique is taken into consideration to help to determine the decision boundaries based upon Gaussian probability model. Hence, the hybrid EDML is developed to provide alternative way to improve the classification accuracy. The objective of this paper is to assess the use of polarimetric data for the image analysis and classification of land use management. It is illustrated using a well-known polarimetric AIRSAR data of San Francisco. In this paper, EDML technique is shown to have a superior result compared to other techniques.</t>
+  </si>
+  <si>
+    <t>The significance of Real-time, biomedical and satellite Image Processing in understanding the objects &amp; application to Computer Vision</t>
+  </si>
+  <si>
+    <t>The Computer Vision is a broader and hottest area of Digital Image Processing with lot of past, ongoing and future research to accomplish the mission of providing visual sense to computers as like human visual system in understanding, processing, classifying, manipulating, and recalling images based on their category. This Paper focus on providing a clear route map in describing the importance of understanding Biomedical, satellite and Real-time photographic Images in application to Computer Vision. The aim of the current research is to Proposes a detailed study on techniques and algorithms proposed by previous researchers and to derive a best and hybrid method that can process all the different category of images and manipulate them for computers to understand the objects clearly as like humans do with the help of supervised/unsupervised algorithms by applying AI techniques.</t>
+  </si>
+  <si>
+    <t>Characterizing Mutual Information Loss in Pyramidal Image Processing Structures</t>
+  </si>
+  <si>
+    <t>Gaussian and Laplacian pyramids have long been important for image analysis and compression. More recently, Gaussian and Laplacian pyramids have become an important component of machine learning and deep learning for image analysis and image recognition. Constructing these pyramids consists of a series of filtering, decimation, and differencing operations, and the quality indicator is usually mean squared reconstruction error in comparison to the original image. We present a new characterization of the information loss in a Gaussian pyramid in terms of the change in mutual information. More specifically, we show that one half the log ratio of entropy powers between two stages in a Gaussian pyramid is equal to the difference in mutual information between these two stages. We show that this relationship holds for a wide variety of probability distributions and present several examples of analyzing Gaussian and Laplacian pyramids for different images.</t>
+  </si>
+  <si>
+    <t>Parallelizing connectivity-based image processing operators in a multi-core environment</t>
+  </si>
+  <si>
+    <t>With increasing computational requirements for state-of-art computer vision and graphics algorithms, multi-core processor implementations have picked up momentum. Adapting single core image processing algorithms for multi-core environment is difficult. Different platforms require a hand tailored approach to optimally fit the algorithm into a given multi-core architecture. An automatic compiler which could split and compile the code for any platform is desirable. Such a compiler doesn't exist and this kind of automation is tough to achieve. To aid existing compilers, we propose a simple software architecture framework for multi-core systems that aims to provide a uniform, scalable, and portable solution, solving specifically for connectivity based image processing operators.</t>
+  </si>
+  <si>
+    <t>Nuclei segmentation of fluorescence microscopy images based on midpoint analysis and marked point process</t>
+  </si>
+  <si>
+    <t>Microscope image analysis is challenging because of non-uniform brightness, decreasing image contrast with tissue depth, poor edge details and irregular and unknown structures. In this paper, we present a nuclei segmentation and counting method using midpoint analysis, shape-based function optimization and a MPP simulation with a spatial birth-death process. Preliminary results demonstrate efficacy of the proposed method.</t>
+  </si>
+  <si>
+    <t>MDL context modeling of images with application to denoising</t>
+  </si>
+  <si>
+    <t>The lately popularized patch-based nonlocal (NL) image processing approach is cast into a framework of statistical context modeling, a thoroughly studied topic in data compression and information theory. The adaptation of image patch (context) to local waveform is crucial to the performance of NL-type of image processing but yet lacks a rigorous study. In this paper we propose a minimum description length (MDL) approach for choosing the size and spatial configuration of the context in which a degraded pixel is to be restored. The MDL criterion of context formation aims to strike an optimal balance between the variance and bias of the errors in fitting a 2D piecewise autoregressive (PAR) model to input image signal. To exemplify the use of the proposed context modeling technique in image processing, an MDL-guided context-based image denoiser is derived and its performance evaluated. Empirical results show that the new context-based denoiser is highly competitive against the current state of the art.</t>
+  </si>
+  <si>
+    <t>Adaptively regularized constrained total least-squares image restoration</t>
+  </si>
+  <si>
+    <t>In this paper, a novel algorithm for image restoration is proposed based on constrained total least-squares (CTLS) estimation, that is, adaptively regularized CTLS (ARCTLS). It is well known that in the regularized CTLS (RCTLS) method, selecting a proper regularization parameter is very difficult. For solving this problem, we take the first-order partial derivative of the classic equation of RCTLS image restoration and do some simplification with it. Then, we deduce an approximate formula, which can be used to adaptively calculate the best regularization parameter along with the degraded image to be restored. We proved that the convergence and the stability of the solution could be well satisfied. The results of our experiments indicate that using this method can make an arbitrary initial parameter be an optimal one, which results in a good restored image of high quality.</t>
+  </si>
+  <si>
+    <t>Real-time automatic spinal level identification with ultrasound image processing</t>
+  </si>
+  <si>
+    <t>In this paper, we propose an ultrasound image processing procedure for fully automatic lumbar spine level identification. The image processing procedure starts with automatic sacrum identification, with feature selection and support vector machine (SVM) classification. After sacrum is detected, a panorama image stitching procedure is initiated to obtain the overall spinous processes structure. Throughout the image stitching and ultrasound probe movement, an image quality evaluation standard is utilized to select the suitable frames to be stitched onto the panorama image, so as to eliminate the accidental bad-quality frames in case the probe goes out-of-line during the scanning movement. In the meantime, the spinous levels are identified and counted on the panorama image, which are then reflected on the original ultrasound image in real time, so as to inform anesthetists where is the level L3-L4 and when to stop scanning. The processing result with off-line collected lumbar ultrasound videos shows a high accuracy on sacrum identification and spinous level identification.</t>
+  </si>
+  <si>
+    <t>Hierarchical image segmentation using adaptive pattern sizes</t>
+  </si>
+  <si>
+    <t>In this paper we propose a method for unsupervised image segmentation, which is suitable for finding the features contained in medical images. The method is based on the hierarchical clustering method in multi-dimensional pattern vector space. We consider to change the size of pattern vectors adaptively to explore useful image features which can be used in medical diagnosis. We have tested our method on the simulation image, which is generated by the Markov Random Field (MRF) model, and the real medical images, photomicrographs of colon tumor, and its effectiveness is confirmed.</t>
+  </si>
+  <si>
+    <t>The application of multiwavelet filterbanks to image processing</t>
+  </si>
+  <si>
+    <t>Multiwavelets are a new addition to the body of wavelet theory. Realizable as matrix-valued filterbanks leading to wavelet bases, multiwavelets offer simultaneous orthogonality, symmetry, and short support, which is not possible with scalar two-channel wavelet systems. After reviewing this theory, we examine the use of multiwavelets in a filterbank setting for discrete-time signal and image processing. Multiwavelets differ from scalar wavelet systems in requiring two or more input streams to the multiwavelet filterbank. We describe two methods (repeated row and approximation/deapproximation) for obtaining such a vector input stream from a one-dimensional (1-D) signal. Algorithms for symmetric extension of signals at boundaries are then developed, and naturally integrated with approximation-based preprocessing. We describe an additional algorithm for multiwavelet processing of two-dimensional (2-D) signals, two rows at a time, and develop a new family of multiwavelets (the constrained pairs) that is well-suited to this approach. This suite of novel techniques is then applied to two basic signal processing problems, denoising via wavelet-shrinkage, and data compression. After developing the approach via model problems in one dimension, we apply multiwavelet processing to images, frequently obtaining performance superior to the comparable scalar wavelet transform.</t>
+  </si>
+  <si>
+    <t>Accelerated 2-D Real-Time Refraction-Corrected Transcranial Ultrasound Imaging</t>
+  </si>
+  <si>
+    <t>In a recent study, we proposed a technique to correct aberration caused by the skull and reconstruct a transcranial B-mode image with a refraction-corrected synthetic aperture imaging (SAI) scheme. Given a sound speed map, the arrival times were calculated using a fast marching technique (FMT), which solves the Eikonal equation and, therefore, is computationally expensive for real-time imaging. In this article, we introduce a two-point ray tracing method, based on Fermat’s principle, for fast calculation of the travel times in the presence of a layered aberrator in front of the ultrasound probe. The ray tracing method along with the reconstruction technique is implemented on a graphical processing unite (GPU). The point spread function (PSF) in a wire phantom image reconstructed with the FMT and the GPU implementation was studied with numerical synthetic data and experiments with a bone-mimicking plate and a sagittally cut human skull. The numerical analysis showed that the error on travel times is less than 10% of the ultrasound temporal period at 2.5 MHz. As a result, the lateral resolution was not significantly degraded compared with images reconstructed with FMT-calculated travel times. The results using the synthetic, bone-mimicking plate, and skull dataset showed that the GPU implementation causes a lateral/axial localization error of 0.10/0.20, 0.15/0.13, and 0.26/0.32 mm compared with a reference measurement (no aberrator in front of the ultrasound probe), respectively. For an imaging depth of 70 mm, the proposed GPU implementation allows reconstructing 19 frames/s with full synthetic aperture (96 transmission events) and 32 frames/s with multiangle plane wave imaging schemes (with 11 steering angles) for a pixel size of 200 μm . Finally, refraction-corrected power Doppler imaging is demonstrated with a string phantom and a bone-mimicking plate placed between the probe and the moving string. The proposed approach achieves a suitable frame rate for clinical scanning while maintaining the image quality.</t>
+  </si>
+  <si>
+    <t>Medical Imaging using Signal Processing: A Comprehensive Review</t>
+  </si>
+  <si>
+    <t>Medical imaging is the technology used to achieve images of the body parts for clinical purposes to determine or analyze the diseases. There are a huge number of imaging methodologies done each day all around the planet. Clinical imaging is turning out to be rapidly developing due to the types of progress in Image Processing (IP) procedures including picture analysis, enhancement, and recognition. IP improves the rate and extent of detected group of cells. Use of image processing methodologies plays a major character in giving assistance to experts in diagnosing, physicians and surgeons and to carry out the surgical procedures for the patients. This paper confers the use of both clear and sophisticated picture evaluation procedures in the clinical imaging field, it sums up how to exemplify image evaluation difficulties using algorithms used by various image processing techniques like k-means, ROI based segmentation, and water-shed strategies and also presents the optimal image processing methodologies which is used in medicals.</t>
+  </si>
+  <si>
+    <t>Introduces a high performance color image scanner which has a variety of digital image processing capabilities such as smooth image reduction and color processing.</t>
+  </si>
+  <si>
+    <t>Digital Image Processing color image scanner</t>
+  </si>
+  <si>
+    <t>Spectral colour image processing</t>
+  </si>
+  <si>
+    <t>Colour is represented as Spectral Power Distribution (SPD) in physical 3D world scene. A set of three discrete values, triplet, such as RGB represents colour in digital 2D image. RGB values are derived from SPD using colour transforms. The physical basis of digital colour is SPD. Colour processing in natural 3D world scene could be thought of manipulation of SPD. We explored different colour enhancement techniques based on derived SPD. Examples showing the spectral based enhancement operations negative, flipping of wavelengths, morphological operations, changing illuminants, increasing the brightness, smoothing, edge detection etc. with experimental results on real images. The results appear to demonstrate that our proposed approach successfully simulates physical processes. Further, the approach outlined in this paper leads to numerous significant applications in computational photography.</t>
+  </si>
+  <si>
+    <t>Comparametric equations with practical applications in quantigraphic image processing</t>
+  </si>
+  <si>
+    <t>It is argued that, hidden within the flow of signals from typical cameras, through image processing, to display media, is a homomorphic filter. While homomorphic filtering is often desirable, there are some occasions where it is not. Thus, cancellation of this implicit homomorphic filter is proposed, through the introduction of an antihomomorphic filter. This concept gives rise to the principle of quantigraphic image processing, wherein it is argued that most cameras can be modeled as an array of idealized light meters each linearly responsive to a semi-monotonic function of the quantity of light received, integrated over a fixed spectral response profile. This quantity depends only on the spectral response of the sensor elements in the camera. A particular class of functional equations, called comparametric equations, is introduced as a basis for quantigraphic image processing. These are fundamental to the analysis and processing of multiple images differing only in exposure. The "gamma correction" of an image is presented as a simple example of a comparametric equation, for which it is shown that the underlying quantigraphic function does not pass through the origin. Thus, it is argued that exposure adjustment by gamma correction is inherently flawed, and alternatives are provided. These alternatives, when applied to a plurality of images that differ only in exposure, give rise to a new kind of processing in the "amplitude domain". The theoretical framework presented in this paper is applicable to the processing of images from nearly all types of modern cameras. This paper is a much revised draft of a 1992 peer-reviewed but unpublished report by the author, entitled "Lightspace and the Wyckoff principle".</t>
+  </si>
+  <si>
+    <t>A CMOS image sensor with programmable pixel-level analog processing</t>
+  </si>
+  <si>
+    <t>A prototype of a 34 /spl times/ 34 pixel image sensor, implementing real-time analog image processing, is presented. Edge detection, motion detection, image amplification, and dynamic-range boosting are executed at pixel level by means of a highly interconnected pixel architecture based on the absolute value of the difference among neighbor pixels. The analog operations are performed over a kernel of 3 /spl times/ 3 pixels. The square pixel, consisting of 30 transistors, has a pitch of 35 /spl mu/m with a fill-factor of 20%. The chip was fabricated in a 0.35 /spl mu/m CMOS technology, and its power consumption is 6 mW with 3.3 V power supply. The device was fully characterized and achieves a dynamic range of 50 dB with a light power density of 150 nW/mm/sup 2/ and a frame rate of 30 frame/s. The measured fixed pattern noise corresponds to 1.1% of the saturation level. The sensor's dynamic range can be extended up to 96 dB using the double-sampling technique.</t>
+  </si>
+  <si>
+    <t>Application of computer image processing technology in Web Design</t>
+  </si>
+  <si>
+    <t>Computer image processing technology is an important part of web design, which can effectively improve the appeal and artistic sense of web page. With the development of the times, the influence of the network in people's life is more and more big, web design has also been widely concerned by people. The application of computer image processing technology in web page design can make the web page more beautiful and efficient. With the continuous improvement of the current society's attention to network publicity, it provides favorable conditions for the combination of art and network development. The application of computer image processing in web design can increase the artistry and attractiveness of web pages, and achieve the purpose of network publicity through the stimulation of people's interest, which can greatly promote the development of the industry. This paper analyzes the web design image processing knowledge and computer image processing technology in the application of web design, for reference only.</t>
+  </si>
+  <si>
+    <t>Research on In-Process Quality Control of Image Digitization</t>
+  </si>
+  <si>
+    <t>In this paper, the author first introduces the concepts and the process of image digitization, then analyzes some theories of in-process quality control, influence factors, critical control point and control method of image digitization, in the final, the author discusses two relevant cases of in-process quality control in image digitization.</t>
+  </si>
+  <si>
+    <t>Image processing in the context of imaging science</t>
+  </si>
+  <si>
+    <t>The rate of discovery in the natural sciences has been accelerated by powerful computer-based imaging methods, which enable scientists to map certain object properties into an 'image space'. These methods also support the goals of medicine, education, art, commerce, and the media. Every digital imaging method involves a sequence of interdependent steps: namely, image-data acquisition, reconstruction and processing, recording and distribution, display/visualization, observation and analysis, and a criterion for image evaluation. When viewed within the context of imaging science, 'optimal' image processing must take account of how the image-data are acquired and the intervening steps leading to how the images are to be evaluated, based on a well-defined goal and criterion.</t>
+  </si>
+  <si>
+    <t>The Use of Undergraduate Project Courses for Teaching Image and Signal Processing Techniques at Purdue University</t>
+  </si>
+  <si>
+    <t>This paper describes our approaches to introduce service learning and research concepts from image and signal processing into the undergraduate ECE curriculum at Purdue University. In particular, we describe two project courses we have developed: one is in the context of the Purdue Engineering Projects in Community Service (EPICS) program and the other is a new course known as Vertically Integrated Projects (VIP). We will describe three projects: EPICS TCHA, EPICS C-SPAN, and VIP Multimedia. These projects provide students, from first-year students to seniors, with the opportunities to integrate real-world solutions and fundamental materials covered in the classroom</t>
+  </si>
+  <si>
+    <t>Remote image processing in a workstation environment</t>
+  </si>
+  <si>
+    <t>Advances in computer networking have opened opportunities for remote image processing, allowing processing tasks to be distributed among specialized nodes. The integrated programming environment, Davis interactive system (DAISY) provides a control panel interface on a workstation to a library of image processing applications that run on specialized remote hosts. The workstation provides an interface to a remote image display, image previews, and an image display.</t>
+  </si>
+  <si>
+    <t>GIS Based System Integrated with Spatial Image Processing Function for Disaster Reduction</t>
+  </si>
+  <si>
+    <t>The disaster reduction systems are most based on GIS, and the core idea of those systems is the past earthquake experiences. Remote sensing image processing can help government assess earthquake damage quickly. Taking this technology integrated with the quondam system can improve the assessment's precision of this kind of system. In this paper, the technology means and prospect of using RS technology to quickly evaluate the earthquake damage have been discussed. Firstly, three earthquake damage cases are presented to show the possibility and problems in quick evaluation of earthquake damage by means of GIS based system. Secondly, a result of Bachu earthquake damage by RS is put forward to illustrate the application prospect of earthquake damage quick assessment. Thirdly, integrating the image processing module with the old system to get the new system REPDRS, in which the assessment's precision can be improved.</t>
+  </si>
+  <si>
+    <t>Infinitely Divisible Cascades to Model the Statistics of Natural Images</t>
+  </si>
+  <si>
+    <t>We propose to model the statistics of natural images, thanks to the large class of stochastic processes called Infinitely Divisible Cascades (IDCs). IDCs were first introduced in one dimension to provide multifractal time series to model the so-called intermittency phenomenon in hydrodynamical turbulence. We have extended the definition of scalar IDCs from one to N dimensions and commented on the relevance of such a model in fully developed turbulence in [1 ]. In this paper, we focus on the particular 2D case. IDCs appear as good candidates to model the statistics of natural images. They share most of their usual properties and appear to be consistent with several independent theoretical and experimental approaches of the literature. We point out the interest of IDCs for applications to procedural texture synthesis.</t>
+  </si>
+  <si>
+    <t>Accurate Whole-Brain Image Enhancement for Low-Dose Integrated PET/MR Imaging Through Spatial Brain Transformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positron emission tomography/magnetic resonance imaging (PET/MRI) systems can provide precise anatomical and functional information with exceptional sensitivity and accuracy for neurological disorder detection. Nevertheless, the radiation exposure risks and economic costs of radiopharmaceuticals may pose significant burdens on patients. To mitigate image quality degradation during low-dose PET imaging, we proposed a novel 3D network equipped with a spatial brain transform (SBF) module for low-dose whole-brain PET and MR images to synthesize high-quality PET images. The FreeSurfer toolkit was applied to derive the spatial brain anatomical alignment information, which was then fused with low-dose PET and MR features through the SBF module. Moreover, several deep learning methods were employed as comparison measures to evaluate the model performance, with the peak signal-to-noise ratio (PSNR), structural similarity (SSIM) and Pearson correlation coefficient (PCC) serving as quantitative metrics. Both the visual results and quantitative results illustrated the effectiveness of our approach. The obtained PSNR and SSIM were 41.96±4.91 dB (p &lt; 0.01) and 0.9654±0.0215 (p &lt; 0.01), which achieved a 19% and 20% improvement, respectively, compared to the original low-dose brain PET images. The volume of interest (VOI) analysis of brain regions such as the left thalamus (PCC = 0.959) also showed that the proposed method could achieve a more accurate standardized uptake value (SUV) distribution while preserving the details of brain structures. In future works, we hope to apply our method to other multimodal systems, such as PET/CT, to assist clinical brain disease diagnosis and treatment.
+</t>
+  </si>
+  <si>
+    <t>A multimodal registration algorithm of eye fundus images using vessels detection and Hough transform</t>
+  </si>
+  <si>
+    <t>Image registration is a real challenge because physicians handle many images. Temporal registration is necessary in order to follow the various steps of a disease, whereas multimodal registration allows us to improve the identification of some lesions or to compare pieces of information gathered from different sources. This paper presents an algorithm for temporal and/or multimodal registration of retinal images based on point correspondence. As an example, the algorithm has been applied to the registration of fluorescein images (obtained after a fluorescein dye injection) with green images (green filter of a color image). The vascular tree is first detected in each type of images and bifurcation points are labeled with surrounding vessel orientations. An angle-based invariant is then computed in order to give a probability for two points to match. Then a Bayesian Hough transform is used to sort the transformations with their respective likelihoods. A precise affine estimate is finally computed for most likely transformations. The best transformation is chosen for registration.</t>
+  </si>
+  <si>
+    <t>A Self-regularized Low-light Image Enhancement Based on the Brightness Information</t>
+  </si>
+  <si>
+    <t>Low-light images have low brightness, low contrast, narrow gray range, color distortion and other problems, resulting in poor visual perception of the image, but also lead to subsequent image recognition, classification and other tasks of the accuracy of the reduction. However, existing low-light image enhancement algorithm has the difficulty of obtaining the training pairing data, and the color recovery of the enhanced image has some problems. In view of the above problems, we propose a self-regularized lowlight image enhancement algorithm based on the brightness information of HSV color space. First it converts low-light images to HSV space, preserves color features (hue, saturation) in lowlight images. Second, builds a brightness enhancement network on the value channel to enhance the brightness characteristics of lowlight images. The brightness enhancement network does not need paired low-light and normal lighting images, but uses non-reference loss function to regularize the network, effectively avoids the problem of over-fitting the label data with the model. Only the single channel of low-light images is enhanced, the computational complexity of the network is low and the computing speed is fast. Experiments show that our method can effectively enhance the low-light image, and can well retain the original color characteristics of the image, reduce the color deviation of the enhanced image, in the objective index and the sense of the supervisor is better than the current multiple method.</t>
+  </si>
+  <si>
+    <t>Robust quantification of in vitro angiogenesis through image analysis</t>
+  </si>
+  <si>
+    <t>An automated image analysis method for quantification of in vitro angiogenesis is presented. The method is designed for in vitro angiogenesis assays that are based on co-culturing endothelial cells with fibroblasts. Such assays are used in many current studies in which anti-angiogenic agents for the treatment of cancer are being sought. This search requires accurate quantification of the stimulatory and inhibitory effects of the different agents. The quantification method gives lengths and sizes of the tubule complexes as well as the numbers of junctions in each of them. The method is tested with a set of test images obtained with a commercially available in vitro angiogenesis assay. The results correctly indicate the inhibitory effect of suramin and the stimulatory effect of vascular endothelial growth factor. Moreover, the image analysis method is shown to be robust against variations in illumination. We have implemented a software package that utilizes the methods. The software as well as a set of test images are available at http://www.cs.tut.fi/sgn/csb/angioquant/.</t>
+  </si>
+  <si>
+    <t>Dynamic Web Service Based Image Processing System</t>
+  </si>
+  <si>
+    <t>This paper introduces a distributed image processing system based on service oriented architecture (SOA). SOA offers considerable flexibility in aligning IT functions and business processes and goals. Each phase in image processing system is viewed as a Web service operated on the Internet. The Web service provides various functions of pre-processing, noise removal, segmentation and feature extraction. Image processing defines algorithms to process 2D &amp; 3D digital images for meaningful interpretation of image content. Each algorithm is implemented as a Web service. Set of algorithms are implemented for each phase and the phases of image processing are linked dynamically. Hence, depending on user's requirement the Web services are dynamically linked using event condition action [ECA] paradigm. We proposed light reference architecture for exposing the image processing system as a Web service on a public network by granting external consumers to access internal services.</t>
+  </si>
+  <si>
+    <t>Embedded co-processor architecture for CMOS based image acquisition</t>
+  </si>
+  <si>
+    <t>This paper describes a new co-processor architecture designed for CMOS sensor imaging. The co-processor unit is integrated into the image acquisition loop so as to exploit the full potential of CMOS selective access imaging technology. The processing features of the co-processor are functional to the specific acquisition process of CMOS sensors (random region acquisition, variable image size, variable acquisition modes line/region based, multiexposition images). Moreover, although built with pipelined or parallel HW processing modules, the co-processor architecture has been designed so as to obtain a unit that can be configured on the fly, in terms of type and number of chained processing, during the image acquisition process that is defined by the application. Simulated performances based on a FPGA implementation, are reported and compared to classical image acquisition systems based on PC platforms.</t>
+  </si>
+  <si>
+    <t>Research and implementation of a digital image processing education platform</t>
+  </si>
+  <si>
+    <t>Digital image processing is an important course, which has strong theoretical and practical needs for students. This paper proposes a digital image processing education platform (DIPEP) based on C# and .NET framework. It has the image processing, analyzing and visualization function. Students can develop and integrate algorithms into the platform quickly and easily. Moreover, algorithm flow application and algorithm management can be applied by students in DIPEP based on workflow technology. Tested by experiments, DIPEP meets the requirement of interface flexibility, information sharing, algorithms safety and efficiency.</t>
+  </si>
+  <si>
+    <t>The Comprehensive Review on Detection of Macro Nutrients Deficiency in Plants Based on The Image Processing Technique</t>
+  </si>
+  <si>
+    <t>Images are a significant source of data and information in agricultural technologies. The use of image processing techniques had important implications for the analysis of smart farm. The analytical system using digital image processing would classify the nutrient deficiency symptoms much prior than a human could identify. This will enable the farmers to adopt appropriate corrective action in time. The paper discusses various methods used in the detection of nutrient deficiencies in plants based on visual images. The image processing techniques have several stages to get the best results in nutrient deficiency detection, namely image acquisition, image enhancement, image segmentation, and feature extraction. Based on the analyses, it is proved that the image processing technology can support the development of farming automation to accomplish the advantages of low price, high efficiency, and high accuracy. Through analysis and discussion, the paper proposed a new technique in every phase of image processing for the detection of nutrient deficiency as the basis of the implementation in future research. Consequently, the research will support the growth of agricultural automation equipment and systems in more smart approaches.</t>
+  </si>
+  <si>
+    <t>Evaluation of the Image Processing Technique in Interpretation of Polar Plot Characteristics of Transformer Frequency Response</t>
+  </si>
+  <si>
+    <t>Frequency response analysis (FRA) is one of the most efficient methods that can diagnose the mechanical faults of power transformers. Digital image processing of the FRA polar plot characteristics has been recently proposed in the literature for the interpretation of power transformers Frequency response. The important advantage of this method is using the phase angle of the FRA trace in addition to its amplitude for the analysis. The digital image processing techniques implemented on the FRA polar plot detect the fault by extracting and analyzing different features of the image by using texture analysis. In this study, the performance of this method is investigated on real windings to examine its ability in detecting the fault extent and type. This step is mandatory since the method is new in the FRA field and has been investigated only in simulation cases. Three different faults, including axial displacement, disk space variation, and radial deformation, are implemented in the experimental setup for the study. Results of implementation of this approach show that this approach neither can determine the fault extent nor the fault type. Therefore, essential changes need to be implemented in the method before applying it in the field.</t>
+  </si>
+  <si>
+    <t>Structure Preserving Image Interpolation via Adaptive 2D Autoregressive Modeling</t>
+  </si>
+  <si>
+    <t>The performance of image interpolation depends on an image model that can adapt to nonstationary statistics of natural images when estimating the missing pixels. However, the construction of such an adaptive model needs the knowledge of every pixels that are absent. We resolve this dilemma by a new piecewise 2D autoregressive technique that builds the model and estimates the missing pixels jointly. This task is formulated as a non-linear optimization problem. Although computationally demanding, the new non-linear approach produces superior results than current methods in both PSNR and subjective visual quality. Moreover, in quest for a practical solution, we break the non-linear optimization problem into two subproblems of linear least-squares estimation. This linear approach proves very effective in our experiments.</t>
+  </si>
+  <si>
+    <t>A Hierarchical Topological Knowledge Based Image Segmentation Approach Optimizing the use of Contextual Regions of Interest : Illustration for Medical Image Analysis</t>
+  </si>
+  <si>
+    <t>This paper concerns image segmentation and presents a method to automically determine optimal regions of interest (ROI) according to topological information. The use of ROI avoids the processing of irrelevant image points, therefore improving and accelerating segmentations. ROI determination is based on the optimal use of both the a priori knowledge about topological structure of an image and the contextual information. Contextual information concerns the nature of already segmented regions in the case of the hierarchical segmentation approach we consider. We describe this general purpose method and propose a formulation for the optimal determination of ROIs according to both informations. Then, we illustrate the use and the implementation of such a method in the particular case of medical image segmentation.</t>
+  </si>
+  <si>
+    <t>A Pupil Diameter Measurement System Based on Image Processing</t>
+  </si>
+  <si>
+    <t>At present, the measurement of pupil diameter is often carried out with specialized medical equipment, combining infrared optical and acoustic methods. However, for the general public, these instruments are often expensive and not worth buying. In order to solve this problem, taking into account that with the gradual popularization of electronic devices, the camera has become a necessary item in the hands of each of us, combined with the current rapid development of image processing technology, we set up an image processing based on the measurement of the pupil diameter system, we through the camera to take pictures of the eye, the use of grayscale conversion, threshold segmentation and other image processing methods, to extract the pupil of the eye region, combined with our size measurement algorithms, the pupil diameter measurement system, and then the pupil diameter measurement algorithm. We extract the pupil area of our human eye by using image processing methods such as gray-to-gray conversion and threshold segmentation. At the same time, because the pupil area obtained from the camera is dynamically changing, we get the dynamically changing value of the pupil diameter of the human eye. It has been exhibited that the pupil of the human eye is not a perfect circle, but is actually closer to an irregular ellipse, so we use the least squares method to fit the pupil contour of the human eye to an ellipse before measurement. In order to improve the accuracy of the final measurement, we calculated the actual length of each pixel in the horizontal and vertical coordinates to complete our final measurement of the pupil diameter.</t>
+  </si>
+  <si>
+    <t>A new embedded image information processing system design</t>
+  </si>
+  <si>
+    <t>today the computer's development has entered the post-PC era, more and more embedded devices have permeated our daily lives, and image processing system based on embedded technology can be used for industrial control, intelligent transportation, residential surveillance and other fields. This paper mainly researches a type of embedded image information acquisition system, including the establishment of system image acquisition tasks, the encoding and storage of captured images, and other treatment methods, mainly including the following sections: the first is to research the real-time display of digital image information on the LCD, the second is to achieve the design of image information storage part in the system through BMP image coding research.</t>
+  </si>
+  <si>
+    <t>CNN-Based Ultrasound Image Reconstruction for Ultrafast Displacement Tracking</t>
+  </si>
+  <si>
+    <t>Thanks to its capability of acquiring full-view frames at multiple kilohertz, ultrafast ultrasound imaging unlocked the analysis of rapidly changing physical phenomena in the human body, with pioneering applications such as ultrasensitive flow imaging in the cardiovascular system or shear-wave elastography. The accuracy achievable with these motion estimation techniques is strongly contingent upon two contradictory requirements: a high quality of consecutive frames and a high frame rate. Indeed, the image quality can usually be improved by increasing the number of steered ultrafast acquisitions, but at the expense of a reduced frame rate and possible motion artifacts. To achieve accurate motion estimation at uncompromised frame rates and immune to motion artifacts, the proposed approach relies on single ultrafast acquisitions to reconstruct high-quality frames and on only two consecutive frames to obtain 2-D displacement estimates. To this end, we deployed a convolutional neural network-based image reconstruction method combined with a speckle tracking algorithm based on cross-correlation. Numerical and in vivo experiments, conducted in the context of plane-wave imaging, demonstrate that the proposed approach is capable of estimating displacements in regions where the presence of side lobe and grating lobe artifacts prevents any displacement estimation with a state-of-the-art technique that relies on conventional delay-and-sum beamforming. The proposed approach may therefore unlock the full potential of ultrafast ultrasound, in applications such as ultrasensitive cardiovascular motion and flow analysis or shear-wave elastography.</t>
+  </si>
+  <si>
+    <t>Research on Crack Size Identification Method Based on Digital Image Processing Technology</t>
+  </si>
+  <si>
+    <t>Cracks is one of the common hazards in offshore structures, and continuous crack propagation can cause serious consequences such as steel structure fracture. The steel structure adopts a regular inspection method to detect structural cracks. Once cracks are found, emergency repair and maintenance work is carried out to ensure the safety of the structure. One of the keys of crack visual inspection is to accurately extract crack size from image. Based on digital image processing technology, the camera calibration, image processing and crack feature extraction were achieved by OpenCV and Skimage open source algorithm package, and then the crack pixel size was extracted. The crack pixel size is converted to the actual size by pixel calibration. The crack length inspection error is 4.8%, and the maximum width inspection error is 13.7%. The results show that the crack identification method has high crack inspection accuracy,which is worth spreading and applying.</t>
+  </si>
+  <si>
+    <t>Joint MR-PET Reconstruction Using a Multi-Channel Image Regularizer</t>
+  </si>
+  <si>
+    <t>While current state of the art MR-PET scanners enable simultaneous MR and PET measurements, the acquired data sets are still usually reconstructed separately. We propose a new multi-modality reconstruction framework using second order Total Generalized Variation (TGV) as a dedicated multi-channel regularization functional that jointly reconstructs images from both modalities. In this way, information about the underlying anatomy is shared during the image reconstruction process while unique differences are preserved. Results from numerical simulations and in-vivo experiments using a range of accelerated MR acquisitions and different MR image contrasts demonstrate improved PET image quality, resolution, and quantitative accuracy.</t>
+  </si>
+  <si>
+    <t>Topological analysis of trabecular bone MR images</t>
+  </si>
+  <si>
+    <t>Recently, imaging techniques have become available which permit nondestructive analysis of the three-dimensional (3-D) architecture of trabecular bone (TB), which forms a network of interconnected plates and rods. Most osteoporotic fractures occur at locations rich in TB, which has spurred the search for architectural parameters as determinants of bone strength. Here, the authors present a new approach to quantitative characterization of the 3-D microarchitecture of TB, based on digital topology. The method classifies each voxel of the 3-D structure based on the connectivity information of neighboring voxels. Following conversion of the 3-D digital image to a skeletonized surface representation containing only one-dimensional (1-D) and two-dimensional (2-D) structures, each voxel is classified as a curve, surface, or junction. The method has been validated by means of synthesized images and has subsequently been applied to TB images from the human wrist. The topological parameters were found to predict Young's modulus (YM) for uniaxial loading, specifically, the surface-to-curve ratio was found to be the single strongest predictor of YM (r/sup 2/=0.69). Finally, the method has been applied to TB images from a group of patients showing very large variations in topological parameters that parallel much smaller changes in bone volume fraction (BVF).</t>
+  </si>
+  <si>
+    <t>Real-time traffic flow detection system based on video image processing</t>
+  </si>
+  <si>
+    <t>With the development of urbanization, traffic problems are becoming more and more serious. Relevant literature shows that traffic information is a direct reflection of road conditions, and timely mastering of traffic information has important research significance for rational allocation of traffic resources and alleviation of congestion. In order to obtain the main traffic information of the road in real time, this paper designed a detection system of vehicle flow and vehicle queue length based on FPGA. Through analyzing the system requirements, and conducting experiments on the development system and simulation tools used, relevant data were obtained. In addition, this paper studies image preprocessing, vehicle presence detection algorithm, vehicle flow statistics algorithm and vehicle queuing length to get relevant conclusions. It provides practical research significance for road traffic resource optimization and traffic light signal lamp.</t>
+  </si>
+  <si>
+    <t>Computation tool to improve teaching-learning process in course of Image Processing in Mechatronic Engineering</t>
+  </si>
+  <si>
+    <t>This article shows the use of a computer tool to improve the teaching-learning process in a learning unit of the Advanced Signal Processing course. This course belongs to the eighth semester of the Mechatronic Engineering Degree, at the Ricardo Palma University, Lima, Peru. Then, with the experience in the dictation of this course for 8 consecutive years, a didactic manual was developed using the Matlab software and the Image Processing Toolbox, with the objective of imparting topics of basic spatial processing, improvement, smoothing, morphological and geometric transformations, and edge detection, depending on the content of the syllable. In this way, the students used the manual as a support to develop simulations such as: pattern recognition, improvement of medical images, etc. Then, with the averages of the evaluations of the laboratory tasks, the performance of the students was represented with a trend graph whose slope was 0.3391.</t>
+  </si>
+  <si>
+    <t>Medical image processing and analysis for nuclear medicine diagnosis</t>
+  </si>
+  <si>
+    <t>The design and implementation of Medical Image Processing and Analysis for Nuclear Medicine Diagnosis on personal computer which was developed using software such as Borland Delphi 6.0 for image processing and analysis. This research provides the following facilities: (1) DICOM viewer which can display various standard formats of digital image data both single frame, multiframes and cine loop such as DICOM, INTERFILE, BITMAP, JPEG and JPEG2000. (2) Image processing which has also the capabilities to zoom in/out and contrast/color map. (3) Image analysis which determine the pixel values in a ROI that can be set up in various forms such as rectangle, ellipse, line and polygon. Thence, Semi-auto ROI setting that sets ROI semi-automatically on region of expected disease. Additionally, more than one ROI can be set in a single image. (4) Nuclear medicine diagnosis which are more functions on nuclear medicine for renal study such as calculation of Glomerular Filtration Rate (GFR), Effective Renal Plasma Flow (ERPF), and plot of the Time Activity Curve or Renogram. Finally, This research was tested with the DICOM 3.0 standard image compared the APEX-XPERT Program. The result showed that no significant difference can be found (α= 0.05).</t>
+  </si>
+  <si>
+    <t>Low-Power Design of Advanced Image Processing Algorithms under FPGA in Real-Time Applications</t>
+  </si>
+  <si>
+    <t>Due to the real-time measurement required for image processing in practice, image processing technology is increasingly supplemented by hardware, such as using DSP (Digital Signal Processing) chips (image processing specific chips). However, when storing and processing large amounts of data, using DSP for image processing also has problems such as slow processing speed and poor real-time performance of the system. This article combines the embedded cache module in the IP core of FPGA (Field Programmable Gate Array) with the read/write ping-pong structure to store and retrieve image data, in order to save memory space on the chip. The relatively simple algorithm functions and parallel computing of FPGA, combined with a pipeline structure, shorten the image preprocessing time and solve the problem of poor real-time image processing. The experimental results show that due to the increase in workload, the static power consumption of FPGA algorithm design only increased from lW to 1.242W, while the static power consumption of traditional design increased from 1.009W to 1.578W; The dynamic power consumption of FPGA algorithm design has increased from 1.005W to 1.489W.</t>
+  </si>
+  <si>
+    <t>Infrared Image Super-Resolution via Transfer Learning and PSRGAN</t>
+  </si>
+  <si>
+    <t>Recent advances in single image super-resolution (SISR) demonstrate the power of deep learning for achieving better performance. Because it is costly to recollect the training data and retrain the model for infrared (IR) image super-resolution, the availability of only a few samples for restoring IR images presents an important challenge in the field of SISR. To solve this problem, we first propose the progressive super-resolution generative adversarial network (PSRGAN) that includes the main path and branch path. The depthwise residual block (DWRB) is used to represent the features of the IR image in the main path. Then, the novel shallow lightweight distillation residual block (SLDRB) is used to extract the features of the readily available visible image in the other path. Furthermore, inspired by transfer learning, we propose the multistage transfer learning strategy for bridging the gap between different high-dimensional feature spaces that can improve the PSGAN performance. Finally, quantitative and qualitative evaluations of two public datasets show that PSRGAN can achieve better results compared to the SR methods.</t>
+  </si>
+  <si>
+    <t>Computer Assistance Image Processing Spores Counting</t>
+  </si>
+  <si>
+    <t>To monitor plant disease which caused by spores, it is needed to obtain the spores image exterior outline characteristic, prepares for spores type analysis and automatic counting. This paper uses computer assistance digital image processing, realized image pretreatment, determined the threshold value reasonably, and transformed the gray image to binary image. Images was captured by CCD and input into computer for process. A kind of gray images research method has been proposed. In order to remove low frequency components, the input gray image is preprocessed by edge enhancement using the Median filter and canny edge algorithm. In this foundation using the imagery processing technology carries on morphology analyses, feature extraction and track. Its goal is obtains the spore image exterior outline characteristic, completes the spores type analysis, counting and distinguish.</t>
+  </si>
+  <si>
+    <t>Towards a diffusion image processing validation and accuracy prediction framework</t>
+  </si>
+  <si>
+    <t>Validation is the main bottleneck preventing the adoption of many medical image processing algorithms in the clinical practice. In the classical approach, a-posteriori analysis is performed based on some objective metrics. In this work, a different approach based on Petri Nets (PN) is proposed. The basic idea consists in predicting the accuracy that will result from a given processing based on the characterization of the sources of inaccuracy of the system. Here we propose a proof of concept in the scenario of a diffusion imaging analysis pipeline. A PN is built after the detection of the possible sources of inaccuracy. By integrating the first qualitative insights based on the PN with quantitative measures, it is possible to optimize the PN itself, to predict the inaccuracy of the system in a different setting. Results show that the proposed model provides a good prediction performance and suggests the optimal processing approach.</t>
+  </si>
+  <si>
+    <t>An algorithm for fast adaptive image binarization with applications in radiotherapy imaging</t>
+  </si>
+  <si>
+    <t>Locally adaptive image binarization with a sliding-window threshold can be an effective tool for various image processing tasks. We have used the method for the detection of bone ridges in radiotherapy portal images. However, a straight-forward implementation of sliding-window processing is too time consuming for routine use. Therefore, we have developed a new thresholding criterion suitable for incremental update within the sliding window, and we show that our algorithm gives better results on difficult portal images than various publicly available adaptive thresholding routines. For small windows, the routine is also faster than an adaptive implementation of the Otsu algorithm that uses interpolation between fixed tiles, and the resulting images are equally good.</t>
+  </si>
+  <si>
+    <t>Integrating visual saliency and consistency for re-ranking image search results</t>
+  </si>
+  <si>
+    <t>The paper investigates two mechanisms, visual consistency and visual saliency, in web image search: (1) In most current web image search engines, such as Google Image Search and Yahoo Image Search, the images that closely related to the search query are typically visually similar. These visually consistent images which occur most frequently in the first few web pages will be given higher ranks. (2) From visual aspect, it is obvious that salient images would be easier to catch users' eyes and more likely to be clicked than the cluttered ones in low-level vision. In addition, we also observe the fact that the visually salient images in the front pages are often relevant to the user's query. The principal novelty of this paper is in combining visual saliency and consistency to re-rank the results from search engines to make the re-ranked images more satisfying in both vision and content. The experimental results on a real world web image dataset demonstrate that our approach can effectively improve the performance of image retrieval.</t>
+  </si>
+  <si>
+    <t>Inpainting Thick Image Regions using Isophote Propagation</t>
+  </si>
+  <si>
+    <t>Most existing methods for inpainting structure images fail in handling thick unknown regions, resulting in over-smoothing effects in the filled areas. In this paper, a novel inpainting algorithm, termed as isophote propagation, is presented to solve the problem. The algorithm propagates isophote information while maintaining the continuity of isophotes directions. It is simple and fast, and performs better in preserving sharp edges than existing algorithms. Effectiveness of the algorithm is demonstrated in experiments.</t>
+  </si>
+  <si>
+    <t>X-Ray Image Processing Methods in Minimally Invasive Spine Surgery</t>
+  </si>
+  <si>
+    <t>In Minimally Invasive Spine Surgery, X-ray image is very important for the whole operation process, which must be monitored though it. For normal X-ray image, the image quality is not clear and the Operation precision is hard to be guaranteed. In this paper, Several image processing methods has been used to enhanced the quality of the picture, Image enhancement and edge detection methods were used to contrast the effect of image processing. The experiment has been used to show the processing results in different surgery procedures. The result indicate the image processing technology can help doctors to improve the operation accuracy effectively.</t>
+  </si>
+  <si>
+    <t>Hardware Up-gradation Plugin for Accelerating the Image Convolution Processing</t>
+  </si>
+  <si>
+    <t>Data collection in the form of Images or videos and its further processing is becoming an inevitable part of many recently developed advanced technology-based devices. For extracting specific and meaningful information from all these large data sets, large computational power is needed. Therefore, the use of heterogeneous system came in to existence in which the existing serial processors are combined with parallel computing processors to produce better output. Most of the applications in image processing have high inherent parallelism. Despite of having low operational frequency FPGAs are capable of generating seemingly high performance by extracting the parallelism to the fullest. In the present manuscript parallel image convolution algorithm is proposed and implemented on FPGA present on Arty Z7 board. The Arty Z7 board can be used as Hardware Up-gradation Plugin (HUP) in hybrid computing systems. The performance of this proposed method is compared with CPU and GPU operating with parallel convolution algorithm. Similarly, it is also compared with serial convolution architecture implemented on FPGA. It is observed that parallel image convolution algorithm consisting of two convolution modules implemented in HUP is producing better results than serial convolution architecture. Further, 8 and 16 parallel convolution modules in HUP performs faster than CPU and GPU for image convolution.</t>
+  </si>
+  <si>
+    <t>The processing and coding of digital image sequences</t>
+  </si>
+  <si>
+    <t>Summary form only given. Digital image processing and coding techniques for application to sequence of images have been examined. Of particular interest are methods applicable to videophones, teleconferencing, and TV broadcasting. One method under development is based on the idea that images are composed of contours, surrounding regions that are (in some sense) uniform. Another technique being developed is based on the extraction of the uniform regions in a sequence, by 3D (split-and-merge) region growing. In this case, the measure of uniformity within a region is the mean-squared error between the image sequence and a 3D approximating polynomial. A given region is coded using the coefficients of the polynomial of best fit and the 3D boundary of the region. The region boundaries are described using a 3D pyramidal structure. Two other methods, both still in the definition stage, are based on conjoint (spatial/spatial-frequency or spatio-temporal/spatio-temporal-frequency) image representations. The final method under consideration is based on the wavelet transform.</t>
+  </si>
+  <si>
+    <t>Local orientation analysis in images by means of the Hermite transform</t>
+  </si>
+  <si>
+    <t>We introduce new theoretical results on how the local differential structure in images can be described, processed, and coded efficiently by means of the Hermite transform. It is shown that the Hermite transform can take many alternative forms, all of which have their specific advantages. The various forms of the Hermite transform correspond to different ways of coding the local orientation in the image, and we describe a systematic theory, based on well-known principles from vector spaces, for deriving such alternative forms. One specific case, called the sampled Hermite transform, is shown to be especially interesting for adaptive image processing and coding. An application in the field of adaptive noise reduction is included by way of illustration.</t>
+  </si>
+  <si>
+    <t>Development and Application of Online Image Processing System Based on Applet and JAI</t>
+  </si>
+  <si>
+    <t>Facing the drawback existing in the stand-alone image processing software, the article proposes a Web-based online image processing software architecture, and make use of the advanced image processing technology of Java Applet and JAI to achieve. Detailed introducing and analysis the programming development method of JAI advanced image processing technology and Applet plug-in implementation process. At the same time, combining the actual research work, Appling the system to the low-resolution remote sensing image distributed processing system, Application results show that the system has a feature of good practicality, multi-platform and security, which can fit different needs of distributed image process.</t>
+  </si>
+  <si>
+    <t>Highly Undersampled Magnetic Resonance Image Reconstruction via Homotopic ℓ0 -Minimization</t>
+  </si>
+  <si>
+    <t>In clinical magnetic resonance imaging (MRI), any reduction in scan time offers a number of potential benefits ranging from high-temporal-rate observation of physiological processes to improvements in patient comfort. Following recent developments in compressive sensing (CS) theory, several authors have demonstrated that certain classes of MR images which possess sparse representations in some transform domain can be accurately reconstructed from very highly undersampled K-space data by solving a convex lscr1-minimization problem. Although lscr1-based techniques are extremely powerful, they inherently require a degree of over-sampling above the theoretical minimum sampling rate to guarantee that exact reconstruction can be achieved. In this paper, we propose a generalization of the CS paradigm based on homotopic approximation of the lscr0 quasi-norm and show how MR image reconstruction can be pushed even further below the Nyquist limit and significantly closer to the theoretical bound. Following a brief review of standard CS methods and the developed theoretical extensions, several example MRI reconstructions from highly undersampled K-space data are presented.</t>
+  </si>
+  <si>
+    <t>3D Image Visual Communication Optimization System on Account of Image Processing Technology</t>
+  </si>
+  <si>
+    <t>As an efficient tool in the new era, computer plays a great role in image processing, video production and development. In the 21st century, the application field of image technology is more extensive, and image technology has also become an important direction of intelligent development. The research on image technology no longer stays in the laboratory. More and more enterprises have also joined the research and application of image technology, and achieved certain results in the fields of object recognition, target tracking, work piece detection and so on. This paper studies the content and knowledge of the design of 3D image visual communication optimization system based on image processing technology, explains the process and technology of film and television image processing and optimization, and expounds the process of system optimization and data analysis in detail. Through the effect analysis of data samples, the test effect shows that with the help of image processing technology, this system has good processing effect in the field of video and image, and has professional processing effect in many aspects of image and video.</t>
+  </si>
+  <si>
+    <t>A review of HDL-based system for real-time image processing used in tumors screening</t>
+  </si>
+  <si>
+    <t>The use of hardware description languages to provide digital image processing results is a recent technique that offers a direct connection to reconfigurable hardware implementation. This paper presents a real time system for digital image processing using Verilog hardware description language that can be followed by immediate hardware implementation possibility. The image enhancement algorithms included in the described system were applied to an ultrasound image. The paper focuses on image enhancement methods such as contrast and brightness transformation, inverting and pseudo-coloring images, described and simulated using Verilog hardware description language. With our study we intend to contribute to the diagnoses of invasive and non-invasive methods in pre-operator stage, using modern VLSI technologies with applications in medical imaging.</t>
+  </si>
+  <si>
+    <t>Expectation maximization reconstruction of positron emission tomography images using anatomical magnetic resonance information</t>
+  </si>
+  <si>
+    <t>Using statistical methods the reconstruction of positron emission tomography (PET) images can be improved by high-resolution anatomical information obtained from magnetic resonance (MR) images. The authors implemented two approaches that utilize MR data for PET reconstruction. The anatomical MR information is modeled as a priori distribution of the PET image and combined with the distribution of the measured PET data to generate the a posteriori function from which the expectation maximization (EM)-type algorithm with a maximum a posteriori (MAP) estimator is derived. One algorithm (Markov-GEM) uses a Gibbs function to model interactions between neighboring pixels within the anatomical regions. The other (Gauss-EM) applies a Gauss function with the same mean for all pixels in a given anatomical region. A basic assumption of these methods is that the radioactivity is homogeneously distributed inside anatomical regions. Simulated and phantom data are investigated under the following aspects: count density, object size, missing anatomical information, and misregistration of the anatomical information. Compared with the maximum likelihood-expectation maximization (ML-EM) algorithm the results of both algorithms show a large reduction of noise with a better delineation of borders. Of the two algorithms tested, the Gauss-EM method is superior in noise reduction (up to 50%). Regarding incorrect a priori information the Gauss-EM algorithm is very sensitive, whereas the Markov-GEM algorithm proved to be stable with a small change of recovery coefficients between 0.5 and 3%.</t>
+  </si>
+  <si>
+    <t>Multi-Center Fetal Brain Tissue Annotation (FeTA) Challenge 2022 Results</t>
+  </si>
+  <si>
+    <t>Segmentation is a critical step in analyzing the developing human fetal brain. There have been vast improvements in automatic segmentation methods in the past several years, and the Fetal Brain Tissue Annotation (FeTA) Challenge 2021 helped to establish an excellent standard of fetal brain segmentation. However, FeTA 2021 was a single center study, limiting real-world clinical applicability and acceptance. The multi-center FeTA Challenge 2022 focused on advancing the generalizability of fetal brain segmentation algorithms for magnetic resonance imaging (MRI). In FeTA 2022, the training dataset contained images and corresponding manually annotated multi-class labels from two imaging centers, and the testing data contained images from these two centers as well as two additional unseen centers. The multi-center data included different MR scanners, imaging parameters, and fetal brain super-resolution algorithms applied. 16 teams participated and 17 algorithms were evaluated. Here, the challenge results are presented, focusing on the generalizability of the submissions. Both in- and out-of-domain, the white matter and ventricles were segmented with the highest accuracy (Top Dice scores: 0.89, 0.87 respectively), while the most challenging structure remains the grey matter (Top Dice score: 0.75) due to anatomical complexity. The top 5 average Dices scores ranged from 0.81-0.82, the top 5 average 95th percentile Hausdorff distance values ranged from 2.3-2.5mm, and the top 5 volumetric similarity scores ranged from 0.90-0.92. The FeTA Challenge 2022 was able to successfully evaluate and advance generalizability of multi-class fetal brain tissue segmentation algorithms for MRI and it continues to benchmark new algorithms.</t>
+  </si>
+  <si>
+    <t>An XML-based process definition language for medical image understanding</t>
+  </si>
+  <si>
+    <t>Medical image understanding is a computing process of object recognition in medical image using computer vision, applied mathematics, signal analysis and artificial intelligence. This paper provides a medical image understanding process definition language (MPDL) which aims at solving the problem of object recognition in medical image and satisfying the requisition of stable and high precision medical image analysis software engineering. MPDL supports coding, debugging, maintenance and share of medical image understanding algorithm. A software component model of medical image understanding algorithm and a mechanism of mapping and synchronization between component and process node in medical image understanding process are represented. The method of validating a medical image understanding process definition is showed in addition. The rationality and applicability of this language is validated by a platform of medical image understanding algorithm development which uses MPDL.</t>
+  </si>
+  <si>
+    <t>Blind Image Super-Resolution via Domain Translation and Diffusion Models</t>
+  </si>
+  <si>
+    <t>Blind image super-resolution is gaining increasing attention due to its significant practical implications. Poor model generalization results from the assumption that low-resolution (LR) images are the consequence of bicubic downsampling of high-resolution (HR) images, which is made by a number of existing super-resolution methods. We employ a degradation model similar to BSRGAN to synthesize LR images, making them appear more realistic, and then treat the blind image super-resolution problem as a domain translation issue, utilizing diffusion models for resolution enhancement.</t>
+  </si>
+  <si>
+    <t>Simple and effective image quality assessment based on edge enhanced mean square error</t>
+  </si>
+  <si>
+    <t>Simple and effective image quality assessment (IQA) method is very desirable in many image and video processing applications, such as coding, transmission, restoration and enhancement. Classic pixel absolute error based objective IQA metrics such as mean square error (MSE) and corresponding peak signal to noise ratio (PSNR) are widely used for various applications due to low computation and clear physical meanings, but have also been criticized for poorly correlated with subjective evaluation. Inspired by that human visual system (HVS) is more sensitive to image local edge distortion than flat or texture areas, in this paper, we propose a novel edge enhanced MSE (EE-MSE) to emphasize edge distortion effects on IQA. Experimental results on LIVE database release 2 show that the proposed EE-MSE IQA metric is competitive with state-of-the-art HVS-based IQA metrics, while has lower computational complexity and is more suitable for optimization task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A brief experience on journey through hardware developments for image
+processing and it’s applications on Cryptography </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The importance of embedded applications on image and video processing, communication and
+cryptography domain has been taking a larger space in current research era. Improvement of
+pictorial information for betterment of human perception like deblurring, de-noising in several fields
+such as satellite imaging, medical imaging etc are renewed research thrust. Specifically we would
+like to elaborate our experience on the significance of computer vision as one of the domains where
+hardware implemented algorithms perform far better than those implemented through software. So
+far embedded design engineers have successfully implemented their designs by means of Application
+Specific Integrated Circuits (ASICs) and/or Digital Signal Processors (DSP), however with the
+advancement of VLSI technology a very powerful hardware device namely the Field Programmable
+Gate Array (FPGA) combining the key advantages of ASICs and DSPs was developed which have the
+possibility of reprogramming making them a very attractive device for rapid prototyping.
+Communication of image and video data in multiple FPGA is no longer far away from the thrust of
+secured transmission among them, and then the relevance of cryptography is indeed unavoidable.
+This paper shows how the Xilinx hardware development platform as well Mathwork’s Matlab can be
+used to develop hardware based computer vision algorithms and its corresponding crypto
+transmission channel between multiple FPGA platform from a system level approach, making it
+favourable for developing a hardware-software co-design environment. </t>
+  </si>
+  <si>
+    <t>MiCo: Multi-image Contrast for Reinforcement Visual Reasoning</t>
+  </si>
+  <si>
+    <t>This work explores enabling Chain-of-Thought (CoT) reasoning to link visual cues across multiple images. A straightforward solution is to adapt rule-based reinforcement learning for Vision-Language Models (VLMs). However, such methods typically rely on manually curated question-answer pairs, which can be particularly challenging when dealing with fine grained visual details and complex logic across images. Inspired by self-supervised visual representation learning, we observe that images contain inherent constraints that can serve as supervision. Based on this insight, we construct image triplets comprising two augmented views of the same image and a third, similar but distinct image. During training, the model is prompted to generate a reasoning process to compare these images (i.e., determine same or different). Then we optimize the model with rule-based reinforcement learning. Due to the high visual similarity and the presence of augmentations, the model must attend to subtle visual changes and perform logical reasoning to succeed. Experiments show that, although trained solely on visual comparison tasks, the learned reasoning ability generalizes effectively to a wide range of questions. Without relying on any human-annotated question-answer pairs, our method achieves significant improvements on multi-image reasoning benchmarks and shows strong performance on general vision tasks.</t>
+  </si>
+  <si>
+    <t>Single-shot HDR using conventional image sensor shutter functions and optical randomization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-dynamic-range (HDR) imaging is an essential technique for overcoming the dynamic range limits of image sensors. The classic method relies on multiple exposures, which slows capture time, resulting in motion artifacts when imaging dynamic scenes. Single-shot HDR imaging alleviates this issue by encoding HDR data into a single exposure, then computationally recovering it. Many established methods use strong image priors to recover improperly exposed image detail. These approaches struggle with extended highlight regions. We utilize the global reset release (GRR) shutter mode of an off-the-shelf sensor. GRR shutter mode applies a longer exposure time to rows closer to the bottom of the sensor. We use optics that relay a randomly permuted (shuffled) image onto the sensor, effectively creating spatially randomized exposures across the scene. The exposure diversity allows us to recover HDR data by solving an optimization problem with a simple total variation image prior. In simulation, we demonstrate that our method outperforms other single-shot methods when many sensor pixels are saturated (10% or more), and is competitive at a modest saturation (1%). Finally, we demonstrate a physical lab prototype that uses an off-the-shelf random fiber bundle for the optical shuffling. The fiber bundle is coupled to a low-cost commercial sensor operating in GRR shutter mode. Our prototype achieves a dynamic range of up to 73dB using an 8-bit sensor with 48dB dynamic range. </t>
+  </si>
+  <si>
+    <t>Dehazing Light Microscopy Images with Guided Conditional Flow Matching: finding a sweet spot between fidelity and realism</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fluorescence microscopy is a major driver of scientific progress in the life sciences. Although high-end confocal microscopes are capable of filtering out-of-focus light, cheaper and more accessible microscopy modalities, such as widefield microscopy, can not, which consequently leads to hazy image data. Computational dehazing is trying to combine the best of both worlds, leading to cheap microscopy but crisp-looking images. The perception-distortion trade-off tells us that we can optimize either for data fidelity, e.g. low MSE or high PSNR, or for data realism, measured by perceptual metrics such as LPIPS or FID. Existing methods either prioritize fidelity at the expense of realism, or produce perceptually convincing results that lack quantitative accuracy. In this work, we propose HazeMatching, a novel iterative method for dehazing light microscopy images, which effectively balances these objectives. Our goal was to find a balanced trade-off between the fidelity of the dehazing results and the realism of individual predictions (samples). We achieve this by adapting the conditional flow matching framework by guiding the generative process with a hazy observation in the conditional velocity field. We evaluate HazeMatching on 5 datasets, covering both synthetic and real data, assessing both distortion and perceptual quality. Our method is compared against 7 baselines, achieving a consistent balance between fidelity and realism on average. Additionally, with calibration analysis, we show that HazeMatching produces well-calibrated predictions. Note that our method does not need an explicit degradation operator to exist, making it easily applicable on real microscopy data. All data used for training and evaluation and our code will be publicly available under a permissive license.</t>
+  </si>
+  <si>
+    <t>A Deep Learning framework for building damage assessment using VHR SAR and geospatial data: demonstration on the 2023 Turkiye Earthquake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building damage identification shortly after a disaster is crucial for guiding emergency response and recovery efforts. Although optical satellite imagery is commonly used for disaster mapping, its effectiveness is often hampered by cloud cover or the absence of pre-event acquisitions. To overcome these challenges, we introduce a novel multimodal deep learning (DL) framework for detecting building damage using single-date very high resolution (VHR) Synthetic Aperture Radar (SAR) imagery from the Italian Space Agency (ASI) COSMO SkyMed (CSK) constellation, complemented by auxiliary geospatial data. Our method integrates SAR image patches, OpenStreetMap (OSM) building footprints, digital surface model (DSM) data, and structural and exposure attributes from the Global Earthquake Model (GEM) to improve detection accuracy and contextual interpretation. Unlike existing approaches that depend on pre and post event imagery, our model utilizes only post event data, facilitating rapid deployment in critical scenarios. The framework effectiveness is demonstrated using a new dataset from the 2023 earthquake in Turkey, covering multiple cities with diverse urban settings. Results highlight that incorporating geospatial features significantly enhances detection performance and generalizability to previously unseen areas. By combining SAR imagery with detailed vulnerability and exposure information, our approach provides reliable and rapid building damage assessments without the dependency from available pre-event data. Moreover, the automated and scalable data generation process ensures the framework's applicability across diverse disaster-affected regions, underscoring its potential to support effective disaster management and recovery efforts. Code and data will be made available upon acceptance of the paper. </t>
+  </si>
+  <si>
+    <t>RoomCraft: Controllable and Complete 3D Indoor Scene Generation</t>
+  </si>
+  <si>
+    <t>Generating realistic 3D indoor scenes from user inputs remains a challenging problem in computer vision and graphics, requiring careful balance of geometric consistency, spatial relationships, and visual realism. While neural generation methods often produce repetitive elements due to limited global spatial reasoning, procedural approaches can leverage constraints for controllable generation but struggle with multi-constraint scenarios. When constraints become numerous, object collisions frequently occur, forcing the removal of furniture items and compromising layout completeness. To address these limitations, we propose RoomCraft, a multi-stage pipeline that converts real images, sketches, or text descriptions into coherent 3D indoor scenes. Our approach combines a scene generation pipeline with a constraint-driven optimization framework. The pipeline first extracts high-level scene information from user inputs and organizes it into a structured format containing room type, furniture items, and spatial relations. It then constructs a spatial relationship network to represent furniture arrangements and generates an optimized placement sequence using a heuristic-based depth-first search (HDFS) algorithm to ensure layout coherence. To handle complex multi-constraint scenarios, we introduce a unified constraint representation that processes both formal specifications and natural language inputs, enabling flexible constraint-oriented adjustments through a comprehensive action space design. Additionally, we propose a Conflict-Aware Positioning Strategy (CAPS) that dynamically adjusts placement weights to minimize furniture collisions and ensure layout completeness. Extensive experiments demonstrate that RoomCraft significantly outperforms existing methods in generating realistic, semantically coherent, and visually appealing room layouts across diverse input modalities.</t>
+  </si>
+  <si>
+    <t>DIGS: Dynamic CBCT Reconstruction using Deformation-Informed 4D Gaussian Splatting and a Low-Rank Free-Form Deformation Model</t>
+  </si>
+  <si>
+    <t>3D Cone-Beam CT (CBCT) is widely used in radiotherapy but suffers from motion artifacts due to breathing. A common clinical approach mitigates this by sorting projections into respiratory phases and reconstructing images per phase, but this does not account for breathing variability. Dynamic CBCT instead reconstructs images at each projection, capturing continuous motion without phase sorting. Recent advancements in 4D Gaussian Splatting (4DGS) offer powerful tools for modeling dynamic scenes, yet their application to dynamic CBCT remains underexplored. Existing 4DGS methods, such as HexPlane, use implicit motion representations, which are computationally expensive. While explicit low-rank motion models have been proposed, they lack spatial regularization, leading to inconsistencies in Gaussian motion. To address these limitations, we introduce a free-form deformation (FFD)-based spatial basis function and a deformation-informed framework that enforces consistency by coupling the temporal evolution of Gaussian's mean position, scale, and rotation under a unified deformation field. We evaluate our approach on six CBCT datasets, demonstrating superior image quality with a 6x speedup over HexPlane. These results highlight the potential of deformation-informed 4DGS for efficient, motion-compensated CBCT reconstruction. The code is available at https://github.com/Yuliang-Huang/DIGS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiovascular disease classification using radiomics and geometric features from cardiac </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic detection and classification of Cardiovascular disease (CVD) from Computed Tomography (CT) images play an important part in facilitating better-informed clinical decisions. However, most of the recent deep learning based methods either directly work on raw CT data or utilize it in pair with anatomical cardiac structure segmentation by training an end-to-end classifier. As such, these approaches become much more difficult to interpret from a clinical perspective. To address this challenge, in this work, we break down the CVD classification pipeline into three components: (i) image segmentation, (ii) image registration, and (iii) downstream CVD classification. Specifically, we utilize the Atlas-ISTN framework and recent segmentation foundational models to generate anatomical structure segmentation and a normative healthy atlas. These are further utilized to extract clinically interpretable radiomic features as well as deformation field based geometric features (through atlas registration) for CVD classification. Our experiments on the publicly available ASOCA dataset show that utilizing these features leads to better CVD classification accuracy (87.50\%) when compared against classification model trained directly on raw CT images (67.50\%). Our code is publicly available: https://github.com/biomedia-mira/grc-net </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose: Aortic dissections are life-threatening cardiovascular conditions requiring accurate segmentation of true lumen (TL), false lumen (FL), and false lumen thrombosis (FLT) from CTA images for effective management. Manual segmentation is time-consuming and variable, necessitating automated solutions. Materials and Methods: We developed four deep learning-based pipelines for Type B aortic dissection segmentation: a single-step model, a sequential model, a sequential multi-task model, and an ensemble model, utilizing 3D U-Net and Swin-UnetR architectures. A dataset of 100 retrospective CTA images was split into training (n=80), validation (n=10), and testing (n=10). Performance was assessed using the Dice Coefficient and Hausdorff Distance. Results: Our approach achieved superior segmentation accuracy, with Dice Coefficients of 0.91  0.07 for TL, 0.88  0.18 for FL, and 0.47  0.25 for FLT, outperforming Yao et al. (1), who reported 0.78  0.20, 0.68  0.18, and 0.25  0.31, respectively. Conclusion: The proposed pipelines provide accurate segmentation of TBAD features, enabling derivation of morphological parameters for surveillance and treatment planning </t>
+  </si>
+  <si>
+    <t>ReF-LLE: Personalized Low-Light Enhancement via Reference-Guided Deep Reinforcement Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Low-light image enhancement presents two primary challenges: 1) Significant variations in low-light images across different conditions, and 2) Enhancement levels influenced by subjective preferences and user intent. To address these issues, we propose ReF-LLE, a novel personalized low-light image enhancement method that operates in the Fourier frequency domain and incorporates deep reinforcement learning. ReF-LLE is the first to integrate deep reinforcement learning into this domain. During training, a zero-reference image evaluation strategy is introduced to score enhanced images, providing reward signals that guide the model to handle varying degrees of low-light conditions effectively. In the inference phase, ReF-LLE employs a personalized adaptive iterative strategy, guided by the zero-frequency component in the Fourier domain, which represents the overall illumination level. This strategy enables the model to adaptively adjust low-light images to align with the illumination distribution of a user-provided reference image, ensuring personalized enhancement results. Extensive experiments on benchmark datasets demonstrate that ReF-LLE outperforms state-of-the-art methods, achieving superior perceptual quality and adaptability in personalized low-light image enhancement. </t>
+  </si>
+  <si>
+    <t>Robust and Accurate Multi-view 2D/3D Image Registration with Differentiable X-ray Rendering and Dual Cross-view Constraints</t>
+  </si>
+  <si>
+    <t>Robust and accurate 2D/3D registration, which aligns preoperative models with intraoperative images of the same anatomy, is crucial for successful interventional navigation. To mitigate the challenge of a limited field of view in single-image intraoperative scenarios, multi-view 2D/3D registration is required by leveraging multiple intraoperative images. In this paper, we propose a novel multi-view 2D/3D rigid registration approach comprising two stages. In the first stage, a combined loss function is designed, incorporating both the differences between predicted and ground-truth poses and the dissimilarities (e.g., normalized cross-correlation) between simulated and observed intraoperative images. More importantly, additional cross-view training loss terms are introduced for both pose and image losses to explicitly enforce cross-view constraints. In the second stage, test-time optimization is performed to refine the estimated poses from the coarse stage. Our method exploits the mutual constraints of multi-view projection poses to enhance the robustness of the registration process. The proposed framework achieves a mean target registration error (mTRE) of  mm on six specimens from the DeepFluoro dataset, demonstrating superior performance compared to state-of-the-art registration algorithms.</t>
+  </si>
+  <si>
+    <t>dreaMLearning: Data Compression Assisted Machine Learning</t>
+  </si>
+  <si>
+    <t>Despite rapid advancements, machine learning, particularly deep learning, is hindered by the need for large amounts of labeled data to learn meaningful patterns without overfitting and immense demands for computation and storage, which motivate research into architectures that can achieve good performance with fewer resources. This paper introduces dreaMLearning, a novel framework that enables learning from compressed data without decompression, built upon Entropy-based Generalized Deduplication (EntroGeDe), an entropy-driven lossless compression method that consolidates information into a compact set of representative samples. DreaMLearning accommodates a wide range of data types, tasks, and model architectures. Extensive experiments on regression and classification tasks with tabular and image data demonstrate that dreaMLearning accelerates training by up to 8.8x, reduces memory usage by 10x, and cuts storage by 42%, with a minimal impact on model performance. These advancements enhance diverse ML applications, including distributed and federated learning, and tinyML on resource-constrained edge devices, unlocking new possibilities for efficient and scalable learning.</t>
+  </si>
+  <si>
+    <t>Q-Frame: Query-aware Frame Selection and Multi-Resolution Adaptation for Video-LLMs</t>
+  </si>
+  <si>
+    <t>Multimodal Large Language Models (MLLMs) have demonstrated significant success in visual understanding tasks. However, challenges persist in adapting these models for video comprehension due to the large volume of data and temporal complexity. Existing Video-LLMs using uniform frame sampling often struggle to capture the query-related crucial spatiotemporal clues of videos effectively. In this paper, we introduce Q-Frame, a novel approach for adaptive frame selection and multi-resolution scaling tailored to the video's content and the specific query. Q-Frame employs a training-free, plug-and-play strategy generated by a text-image matching network like CLIP, utilizing the Gumbel-Max trick for efficient frame selection. Q-Frame allows Video-LLMs to process more frames without exceeding computational limits, thereby preserving critical temporal and spatial information. We demonstrate Q-Frame's effectiveness through extensive experiments on benchmark datasets, including MLVU, LongVideoBench, and Video-MME, illustrating its superiority over existing methods and its applicability across various video understanding tasks.</t>
+  </si>
+  <si>
+    <t>Reasoning in machine vision: learning to think fast and slow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reasoning is a hallmark of human intelligence, enabling adaptive decision-making in complex and unfamiliar scenarios. In contrast, machine intelligence remains bound to training data, lacking the ability to dynamically refine solutions at inference time. While some recent advances have explored reasoning in machines, these efforts are largely limited to verbal domains such as mathematical problem-solving, where explicit rules govern step-by-step reasoning. Other critical real-world tasks - including visual perception, spatial reasoning, and radiological diagnosis - require non-verbal reasoning, which remains an open challenge. Here we present a novel learning paradigm that enables machine reasoning in vision by allowing performance improvement with increasing thinking time (inference-time compute), even under conditions where labelled data is very limited. Inspired by dual-process theories of human cognition in psychology, our approach integrates a fast-thinking System I module for familiar tasks, with a slow-thinking System II module that iteratively refines solutions using self-play reinforcement learning. This paradigm mimics human reasoning by proposing, competing over, and refining solutions in data-scarce scenarios. We demonstrate superior performance through extended thinking time, compared not only to large-scale supervised learning but also foundation models and even human experts, in real-world vision tasks. These tasks include computer-vision benchmarks and cancer localisation on medical images across five organs, showcasing transformative potential for non-verbal machine reasoning. </t>
+  </si>
+  <si>
+    <t>MirrorMe: Towards Realtime and High Fidelity Audio-Driven Halfbody Animation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audio-driven portrait animation, which synthesizes realistic videos from reference images using audio signals, faces significant challenges in real-time generation of high-fidelity, temporally coherent animations. While recent diffusion-based methods improve generation quality by integrating audio into denoising processes, their reliance on frame-by-frame UNet architectures introduces prohibitive latency and struggles with temporal consistency. This paper introduces MirrorMe, a real-time, controllable framework built on the LTX video model, a diffusion transformer that compresses video spatially and temporally for efficient latent space denoising. To address LTX's trade-offs between compression and semantic fidelity, we propose three innovations: 1. A reference identity injection mechanism via VAE-encoded image concatenation and self-attention, ensuring identity consistency; 2. A causal audio encoder and adapter tailored to LTX's temporal structure, enabling precise audio-expression synchronization; and 3. A progressive training strategy combining close-up facial training, half-body synthesis with facial masking, and hand pose integration for enhanced gesture control. Extensive experiments on the EMTD Benchmark demonstrate MirrorMe's state-of-the-art performance in fidelity, lip-sync accuracy, and temporal stability. </t>
+  </si>
+  <si>
+    <t>Towards Scalable and Robust White Matter Lesion Localization via Multimodal Deep Learning</t>
+  </si>
+  <si>
+    <t>White matter hyperintensities (WMH) are radiological markers of small vessel disease and neurodegeneration, whose accurate segmentation and spatial localization are crucial for diagnosis and monitoring. While multimodal MRI offers complementary contrasts for detecting and contextualizing WM lesions, existing approaches often lack flexibility in handling missing modalities and fail to integrate anatomical localization efficiently. We propose a deep learning framework for WM lesion segmentation and localization that operates directly in native space using single- and multi-modal MRI inputs. Our study evaluates four input configurations: FLAIR-only, T1-only, concatenated FLAIR and T1, and a modality-interchangeable setup. It further introduces a multi-task model for jointly predicting lesion and anatomical region masks to estimate region-wise lesion burden. Experiments conducted on the MICCAI WMH Segmentation Challenge dataset demonstrate that multimodal input significantly improves the segmentation performance, outperforming unimodal models. While the modality-interchangeable setting trades accuracy for robustness, it enables inference in cases with missing modalities. Joint lesion-region segmentation using multi-task learning was less effective than separate models, suggesting representational conflict between tasks. Our findings highlight the utility of multimodal fusion for accurate and robust WMH analysis, and the potential of joint modeling for integrated predictions.</t>
+  </si>
+  <si>
+    <t>Noise-Inspired Diffusion Model for Generalizable Low-Dose CT Reconstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The generalization of deep learning-based low-dose computed tomography (CT) reconstruction models to doses unseen in the training data is important and remains challenging. Previous efforts heavily rely on paired data to improve the generalization performance and robustness through collecting either diverse CT data for re-training or a few test data for fine-tuning. Recently, diffusion models have shown promising and generalizable performance in low-dose CT (LDCT) reconstruction, however, they may produce unrealistic structures due to the CT image noise deviating from Gaussian distribution and imprecise prior information from the guidance of noisy LDCT images. In this paper, we propose a noise-inspired diffusion model for generalizable LDCT reconstruction, termed NEED, which tailors diffusion models for noise characteristics of each domain. First, we propose a novel shifted Poisson diffusion model to denoise projection data, which aligns the diffusion process with the noise model in pre-log LDCT projections. Second, we devise a doubly guided diffusion model to refine reconstructed images, which leverages LDCT images and initial reconstructions to more accurately locate prior information and enhance reconstruction fidelity. By cascading these two diffusion models for dual-domain reconstruction, our NEED requires only normal-dose data for training and can be effectively extended to various unseen dose levels during testing via a time step matching strategy. Extensive qualitative, quantitative, and segmentation-based evaluations on two datasets demonstrate that our NEED consistently outperforms state-of-the-art methods in reconstruction and generalization performance. Source code is made available at https://github.com/qgao21/NEED. </t>
+  </si>
+  <si>
+    <t>StableCodec: Taming One-Step Diffusion for Extreme Image Compression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusion-based image compression has shown remarkable potential for achieving ultra-low bitrate coding (less than 0.05 bits per pixel) with high realism, by leveraging the generative priors of large pre-trained text-to-image diffusion models. However, current approaches require a large number of denoising steps at the decoder to generate realistic results under extreme bitrate constraints, limiting their application in real-time compression scenarios. Additionally, these methods often sacrifice reconstruction fidelity, as diffusion models typically fail to guarantee pixel-level consistency. To address these challenges, we introduce StableCodec, which enables one-step diffusion for high-fidelity and high-realism extreme image compression with improved coding efficiency. To achieve ultra-low bitrates, we first develop an efficient Deep Compression Latent Codec to transmit a noisy latent representation for a single-step denoising process. We then propose a Dual-Branch Coding Structure, consisting of a pair of auxiliary encoder and decoder, to enhance reconstruction fidelity. Furthermore, we adopt end-to-end optimization with joint bitrate and pixel-level constraints. Extensive experiments on the CLIC 2020, DIV2K, and Kodak dataset demonstrate that StableCodec outperforms existing methods in terms of FID, KID and DISTS by a significant margin, even at bitrates as low as 0.005 bits per pixel, while maintaining strong fidelity. Additionally, StableCodec achieves inference speeds comparable to mainstream transform coding schemes. All source code are available at https://github.com/LuizScarlet/StableCodec. </t>
+  </si>
+  <si>
+    <t>SDRNET: Stacked Deep Residual Network for Accurate Semantic Segmentation of Fine-Resolution Remotely Sensed Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land cover maps generated from semantic segmentation of high-resolution remotely sensed images have drawn mucon in the photogrammetry and remote sensing research community. Currently, massive fine-resolution remotely sensed (FRRS) images acquired by improving sensing and imaging technologies become available. However, accurate semantic segmentation of such FRRS images is greatly affected by substantial class disparities, the invisibility of key ground objects due to occlusion, and object size variation. Despite the extraordinary potential in deep convolutional neural networks (DCNNs) in image feature learning and representation, extracting sufficient features from FRRS images for accurate semantic segmentation is still challenging. These challenges demand the deep learning models to learn robust features and generate sufficient feature descriptors. Specifically, learning multi-contextual features to guarantee adequate coverage of varied object sizes from the ground scene and harnessing global-local contexts to overcome class disparities challenge even profound networks. Deeper networks significantly lose spatial details due to gradual downsampling processes resulting in poor segmentation results and coarse boundaries. This article presents a stacked deep residual network (SDRNet) for semantic segmentation from FRRS images. The proposed framework utilizes two stacked encoder-decoder networks to harness long-range semantics yet preserve spatial information and dilated residual blocks (DRB) between each encoder and decoder network to capture sufficient global dependencies thus improving segmentation performance. Our experimental results obtained using the ISPRS Vaihingen and Potsdam datasets demonstrate that the SDRNet performs effectively and competitively against current DCNNs in semantic segmentation. </t>
+  </si>
+  <si>
+    <t>Quality Assessment and Distortion-aware Saliency Prediction for AI-Generated Omnidirectional Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> With the rapid advancement of Artificial Intelligence Generated Content (AIGC) techniques, AI generated images (AIGIs) have attracted widespread attention, among which AI generated omnidirectional images (AIGODIs) hold significant potential for Virtual Reality (VR) and Augmented Reality (AR) applications. AI generated omnidirectional images exhibit unique quality issues, however, research on the quality assessment and optimization of AI-generated omnidirectional images is still lacking. To this end, this work first studies the quality assessment and distortion-aware saliency prediction problems for AIGODIs, and further presents a corresponding optimization process. Specifically, we first establish a comprehensive database to reflect human feedback for AI-generated omnidirectionals, termed OHF2024, which includes both subjective quality ratings evaluated from three perspectives and distortion-aware salient regions. Based on the constructed OHF2024 database, we propose two models with shared encoders based on the BLIP-2 model to evaluate the human visual experience and predict distortion-aware saliency for AI-generated omnidirectional images, which are named as BLIP2OIQA and BLIP2OISal, respectively. Finally, based on the proposed models, we present an automatic optimization process that utilizes the predicted visual experience scores and distortion regions to further enhance the visual quality of an AI-generated omnidirectional image. Extensive experiments show that our BLIP2OIQA model and BLIP2OISal model achieve state-of-the-art (SOTA) results in the human visual experience evaluation task and the distortion-aware saliency prediction task for AI generated omnidirectional images, and can be effectively used in the optimization process. The database and codes will be released on https://github.com/IntMeGroup/AIGCOIQA to facilitate future research.</t>
+  </si>
+  <si>
+    <t>TOAST: Task-Oriented Adaptive Semantic Transmission over Dynamic Wireless Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The evolution toward 6G networks demands a fundamental shift from bit-centric transmission to semantic-aware communication that emphasizes task-relevant information. This work introduces TOAST (Task-Oriented Adaptive Semantic Transmission), a unified framework designed to address the core challenge of multi-task optimization in dynamic wireless environments through three complementary components. First, we formulate adaptive task balancing as a Markov decision process, employing deep reinforcement learning to dynamically adjust the trade-off between image reconstruction fidelity and semantic classification accuracy based on real-time channel conditions. Second, we integrate module-specific Low-Rank Adaptation (LoRA) mechanisms throughout our Swin Transformer-based joint source-channel coding architecture, enabling parameter-efficient fine-tuning that dramatically reduces adaptation overhead while maintaining full performance across diverse channel impairments including Additive White Gaussian Noise (AWGN), fading, phase noise, and impulse interference. Third, we incorporate an Elucidating diffusion model that operates in the latent space to restore features corrupted by channel noises, providing substantial quality improvements compared to baseline approaches. Extensive experiments across multiple datasets demonstrate that TOAST achieves superior performance compared to baseline approaches, with significant improvements in both classification accuracy and reconstruction quality at low Signal-to-Noise Ratio (SNR) conditions while maintaining robust performance across all tested scenarios. </t>
+  </si>
+  <si>
+    <t>Interactive Multi-Objective Probabilistic Preference Learning with Soft and Hard Bounds</t>
+  </si>
+  <si>
+    <t>High-stakes decision-making involves navigating multiple competing objectives with expensive evaluations. For instance, in brachytherapy, clinicians must balance maximizing tumor coverage (e.g., an aspirational target or soft bound of &gt;95% coverage) against strict organ dose limits (e.g., a non-negotiable hard bound of &lt;601 cGy to the bladder), with each plan evaluation being resource-intensive. Selecting Pareto-optimal solutions that match implicit preferences is challenging, as exhaustive Pareto frontier exploration is computationally and cognitively prohibitive, necessitating interactive frameworks to guide users. While decision-makers (DMs) often possess domain knowledge to narrow the search via such soft-hard bounds, current methods often lack systematic approaches to iteratively refine these multi-faceted preference structures. Critically, DMs must trust their final decision, confident they haven't missed superior alternatives; this trust is paramount in high-consequence scenarios. We present Active-MoSH, an interactive local-global framework designed for this process. Its local component integrates soft-hard bounds with probabilistic preference learning, maintaining distributions over DM preferences and bounds for adaptive Pareto subset refinement. This is guided by an active sampling strategy optimizing exploration-exploitation while minimizing cognitive burden. To build DM trust, Active-MoSH's global component, T-MoSH, leverages multi-objective sensitivity analysis to identify potentially overlooked, high-value points beyond immediate feedback. We demonstrate Active-MoSH's performance benefits through diverse synthetic and real-world applications. A user study on AI-generated image selection further validates our hypotheses regarding the framework's ability to improve convergence, enhance DM trust, and provide expressive preference articulation, enabling more effective DMs.</t>
+  </si>
+  <si>
+    <t>GRASP-PsONet: Gradient-based Removal of Spurious Patterns for PsOriasis Severity Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Psoriasis (PsO) severity scoring is important for clinical trials but is hindered by inter-rater variability and the burden of in person clinical evaluation. Remote imaging using patient captured mobile photos offers scalability but introduces challenges, such as variation in lighting, background, and device quality that are often imperceptible to humans but can impact model performance. These factors, along with inconsistencies in dermatologist annotations, reduce the reliability of automated severity scoring. We propose a framework to automatically flag problematic training images that introduce spurious correlations which degrade model generalization, using a gradient based interpretability approach. By tracing the gradients of misclassified validation images, we detect training samples where model errors align with inconsistently rated examples or are affected by subtle, nonclinical artifacts. We apply this method to a ConvNeXT based weakly supervised model designed to classify PsO severity from phone images. Removing 8.2% of flagged images improves model AUC-ROC by 5% (85% to 90%) on a held out test set. Commonly, multiple annotators and an adjudication process ensure annotation accuracy, which is expensive and time consuming. Our method detects training images with annotation inconsistencies, potentially removing the need for manual review. When applied to a subset of training data rated by two dermatologists, the method identifies over 90% of cases with inter-rater disagreement by reviewing only the top 30% of samples. This improves automated scoring for remote assessments, ensuring robustness despite data collection variability. </t>
+  </si>
+  <si>
+    <t>Physical Degradation Model-Guided Interferometric Hyperspectral Reconstruction with Unfolding Transformer</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interferometric Hyperspectral Imaging (IHI) is a critical technique for large-scale remote sensing tasks due to its advantages in flux and spectral resolution. However, IHI is susceptible to complex errors arising from imaging steps, and its quality is limited by existing signal processing-based reconstruction algorithms. Two key challenges hinder performance enhancement: 1) the lack of training datasets. 2) the difficulty in eliminating IHI-specific degradation components through learning-based methods. To address these challenges, we propose a novel IHI reconstruction pipeline. First, based on imaging physics and radiometric calibration data, we establish a simplified yet accurate IHI degradation model and a parameter estimation method. This model enables the synthesis of realistic IHI training datasets from hyperspectral images (HSIs), bridging the gap between IHI reconstruction and deep learning. Second, we design the Interferometric Hyperspectral Reconstruction Unfolding Transformer (IHRUT), which achieves effective spectral correction and detail restoration through a stripe-pattern enhancement mechanism and a spatial-spectral transformer architecture. Experimental results demonstrate the superior performance and generalization capability of our method.</t>
+  </si>
+  <si>
+    <t>Remote Sensing Large Vision-Language Model: Semantic-augmented Multi-level Alignment and Semantic-aware Expert Modeling</t>
+  </si>
+  <si>
+    <t>Large Vision and Language Models (LVLMs) have shown strong performance across various vision-language tasks in natural image domains. However, their application to remote sensing (RS) remains underexplored due to significant domain differences in visual appearances, object scales, and semantics. These discrepancies hider the effective understanding of RS scenes, which contain rich, multi-level semantic information spanning from coarse-to-fine levels. Hence, it limits the direct adaptation of existing LVLMs to RS imagery. To address this gap, we propose a novel LVLM framework tailored for RS understanding, incorporating two core components: Semantic-augmented Multi-level Alignment and Semantic-aware Expert Modeling. First, to align multi-level visual features, we introduce the retrieval-based Semantic Augmentation Module which enriches the visual features with relevant semantics across fine-to-coarse levels (e.g., object- and scene-level information). It is designed to retrieve relevant semantic cues from a RS semantic knowledge database, followed by aggregation of semantic cues with user query and multi-level visual features, resulting in semantically enriched representation across multiple levels. Second, for Semantic-aware Expert Modeling, we design semantic experts, where each expert is responsible for processing semantic representation at different levels separately. This enables hierarchical semantic understanding from coarse to fine levels. Evaluations across multiple RS tasks-including scene classification and VQA, etc.-demonstrate that the proposed framework achieves consistent improvements across multiple semantic levels. This highlights its capability and effectiveness in bridging the gap between general LVLMs and unique demands of RS-specific vision-language understanding</t>
+  </si>
+  <si>
+    <t>End-to-End RGB-IR Joint Image Compression With Channel-wise Cross-modality Entropy Model</t>
+  </si>
+  <si>
+    <t>RGB-IR(RGB-Infrared) image pairs are frequently applied simultaneously in various applications like intelligent surveillance. However, as the number of modalities increases, the required data storage and transmission costs also double. Therefore, efficient RGB-IR data compression is essential. This work proposes a joint compression framework for RGB-IR image pair. Specifically, to fully utilize cross-modality prior information for accurate context probability modeling within and between modalities, we propose a Channel-wise Cross-modality Entropy Model (CCEM). Among CCEM, a Low-frequency Context Extraction Block (LCEB) and a Low-frequency Context Fusion Block (LCFB) are designed for extracting and aggregating the global low-frequency information from both modalities, which assist the model in predicting entropy parameters more accurately. Experimental results demonstrate that our approach outperforms existing RGB-IR image pair and single-modality compression methods on LLVIP and KAIST datasets. For instance, the proposed framework achieves a 23.1% bit rate saving on LLVIP dataset compared to the state-of-the-art RGB-IR image codec presented at CVPR 202</t>
+  </si>
+  <si>
+    <t>3D-Telepathy: Reconstructing 3D Objects from EEG Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reconstructing 3D visual stimuli from Electroencephalography (EEG) data holds significant potential for applications in Brain-Computer Interfaces (BCIs) and aiding individuals with communication disorders. Traditionally, efforts have focused on converting brain activity into 2D images, neglecting the translation of EEG data into 3D objects. This limitation is noteworthy, as the human brain inherently processes three-dimensional spatial information regardless of whether observing 2D images or the real world. The neural activities captured by EEG contain rich spatial information that is inevitably lost when reconstructing only 2D images, thus limiting its practical applications in BCI. The transition from EEG data to 3D object reconstruction faces considerable obstacles. These include the presence of extensive noise within EEG signals and a scarcity of datasets that include both EEG and 3D information, which complicates the extraction process of 3D visual data. Addressing this challenging task, we propose an innovative EEG encoder architecture that integrates a dual self-attention mechanism. We use a hybrid training strategy to train the EEG Encoder, which includes cross-attention, contrastive learning, and self-supervised learning techniques. Additionally, by employing stable diffusion as a prior distribution and utilizing Variational Score Distillation to train a neural radiation field, we successfully generate 3D objects with similar content and structure from EEG data. </t>
+  </si>
+  <si>
+    <t>PrefPaint: Enhancing Image Inpainting through Expert Human Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inpainting, the process of filling missing or corrupted image parts, has broad applications, including medical imaging. However, in specialized fields like medical polyps imaging, where accuracy and reliability are critical, inpainting models can generate inaccurate images, leading to significant errors in medical diagnosis and treatment. To ensure reliability, medical images should be annotated by experts like oncologists for effective model training. We propose PrefPaint, an approach that incorporates human feedback into the training process of Stable Diffusion Inpainting, bypassing the need for computationally expensive reward models. In addition, we develop a web-based interface streamlines training, fine-tuning, and inference. This interactive interface provides a smooth and intuitive user experience, making it easier to offer feedback and manage the fine-tuning process. User study on various domains shows that PrefPaint outperforms existing methods, reducing visual inconsistencies and improving image rendering, particularly in medical contexts, where our model generates more realistic polyps images.</t>
+  </si>
+  <si>
+    <t>TaleForge: Interactive Multimodal System for Personalized Story Creation</t>
+  </si>
+  <si>
+    <t>Storytelling is a deeply personal and creative process, yet existing methods often treat users as passive consumers, offering generic plots with limited personalization. This undermines engagement and immersion, especially where individual style or appearance is crucial. We introduce TaleForge, a personalized story-generation system that integrates large language models (LLMs) and text-to-image diffusion to embed users' facial images within both narratives and illustrations. TaleForge features three interconnected modules: Story Generation, where LLMs create narratives and character descriptions from user prompts; Personalized Image Generation, merging users' faces and outfit choices into character illustrations; and Background Generation, creating scene backdrops that incorporate personalized characters. A user study demonstrated heightened engagement and ownership when individuals appeared as protagonists. Participants praised the system's real-time previews and intuitive controls, though they requested finer narrative editing tools. TaleForge advances multimodal storytelling by aligning personalized text and imagery to create immersive, user-centric experiences.</t>
+  </si>
+  <si>
+    <t>TUS-REC2024: A Challenge to Reconstruct 3D Freehand Ultrasound Without External Tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trackerless freehand ultrasound reconstruction aims to reconstruct 3D volumes from sequences of 2D ultrasound images without relying on external tracking systems, offering a low-cost, portable, and widely deployable alternative for volumetric imaging. However, it presents significant challenges, including accurate inter-frame motion estimation, minimisation of drift accumulation over long sequences, and generalisability across scanning protocols. The TUS-REC2024 Challenge was established to benchmark and accelerate progress in trackerless 3D ultrasound reconstruction by providing a publicly available dataset for the first time, along with a baseline model and evaluation framework. The Challenge attracted over 43 registered teams, of which 6 teams submitted 21 valid dockerized solutions. Submitted methods spanned a wide range of algorithmic approaches, including recurrent models, registration-driven volume refinement, attention, and physics-informed models. This paper presents an overview of the Challenge design, summarises the key characteristics of the dataset, provides a concise literature review, introduces the technical details of the underlying methodology working with tracked freehand ultrasound data, and offers a comparative analysis of submitted methods across multiple evaluation metrics. The results highlight both the progress and current limitations of state-of-the-art approaches in this domain, and inform directions for future research. The data, evaluation code, and baseline are publicly available to facilitate ongoing development and reproducibility. As a live and evolving benchmark, this Challenge is designed to be continuously developed and improved. The Challenge was held at MICCAI 2024 and will be organised again at MICCAI 2025, reflecting its growing impact and the sustained commitment to advancing this field. </t>
+  </si>
+  <si>
+    <t>Elucidating and Endowing the Diffusion Training Paradigm for General Image Restoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> While diffusion models demonstrate strong generative capabilities in image restoration (IR) tasks, their complex architectures and iterative processes limit their practical application compared to mainstream reconstruction-based general ordinary IR networks. Existing approaches primarily focus on optimizing network architecture and diffusion paths but overlook the integration of the diffusion training paradigm within general ordinary IR frameworks. To address these challenges, this paper elucidates key principles for adapting the diffusion training paradigm to general IR training through systematic analysis of time-step dependencies, network hierarchies, noise-level relationships, and multi-restoration task correlations, proposing a new IR framework supported by diffusion-based training. To enable IR networks to simultaneously restore images and model generative representations, we introduce a series of regularization strategies that align diffusion objectives with IR tasks, improving generalization in single-task scenarios. Furthermore, recognizing that diffusion-based generation exerts varying influences across different IR tasks, we develop an incremental training paradigm and task-specific adaptors, further enhancing performance in multi-task unified IR. Experiments demonstrate that our method significantly improves the generalization of IR networks in single-task IR and achieves superior performance in multi-task unified IR. Notably, the proposed framework can be seamlessly integrated into existing general IR architectures. </t>
+  </si>
+  <si>
+    <t>TanDiT: Tangent-Plane Diffusion Transformer for High-Quality 360° Panorama Generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recent advances in image generation have led to remarkable improvements in synthesizing perspective images. However, these models still struggle with panoramic image generation due to unique challenges, including varying levels of geometric distortion and the requirement for seamless loop-consistency. To address these issues while leveraging the strengths of the existing models, we introduce TanDiT, a method that synthesizes panoramic scenes by generating grids of tangent-plane images covering the entire 360 view. Unlike previous methods relying on multiple diffusion branches, TanDiT utilizes a unified diffusion model trained to produce these tangent-plane images simultaneously within a single denoising iteration. Furthermore, we propose a model-agnostic post-processing step specifically designed to enhance global coherence across the generated panoramas. To accurately assess panoramic image quality, we also present two specialized metrics, TangentIS and TangentFID, and provide a comprehensive benchmark comprising captioned panoramic datasets and standardized evaluation scripts. Extensive experiments demonstrate that our method generalizes effectively beyond its training data, robustly interprets detailed and complex text prompts, and seamlessly integrates with various generative models to yield high-quality, diverse panoramic images.</t>
+  </si>
+  <si>
+    <t>PhotonSplat: 3D Scene Reconstruction and Colorization from SPAD Sensors</t>
+  </si>
+  <si>
+    <t>Advances in 3D reconstruction using neural rendering have enabled high-quality 3D capture. However, they often fail when the input imagery is corrupted by motion blur, due to fast motion of the camera or the objects in the scene. This work advances neural rendering techniques in such scenarios by using single-photon avalanche diode (SPAD) arrays, an emerging sensing technology capable of sensing images at extremely high speeds. However, the use of SPADs presents its own set of unique challenges in the form of binary images, that are driven by stochastic photon arrivals. To address this, we introduce PhotonSplat, a framework designed to reconstruct 3D scenes directly from SPAD binary images, effectively navigating the noise vs. blur trade-off. Our approach incorporates a novel 3D spatial filtering technique to reduce noise in the renderings. The framework also supports both no-reference using generative priors and reference-based colorization from a single blurry image, enabling downstream applications such as segmentation, object detection and appearance editing tasks. Additionally, we extend our method to incorporate dynamic scene representations, making it suitable for scenes with moving objects. We further contribute PhotonScenes, a real-world multi-view dataset captured with the SPAD sensors.</t>
+  </si>
+  <si>
+    <t>Real-Time 3D Guidewire Reconstruction from Intraoperative DSA Images for Robot-Assisted Endovascular Interventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accurate three-dimensional (3D) reconstruction of guidewire shapes is crucial for precise navigation in robot-assisted endovascular interventions. Conventional 2D Digital Subtraction Angiography (DSA) is limited by the absence of depth information, leading to spatial ambiguities that hinder reliable guidewire shape sensing. This paper introduces a novel multimodal framework for real-time 3D guidewire reconstruction, combining preoperative 3D Computed Tomography Angiography (CTA) with intraoperative 2D DSA images. The method utilizes robust feature extraction to address noise and distortion in 2D DSA data, followed by deformable image registration to align the 2D projections with the 3D CTA model. Subsequently, the inverse projection algorithm reconstructs the 3D guidewire shape, providing real-time, accurate spatial information. This framework significantly enhances spatial awareness for robotic-assisted endovascular procedures, effectively bridging the gap between preoperative planning and intraoperative execution. The system demonstrates notable improvements in real-time processing speed, reconstruction accuracy, and computational efficiency. The proposed method achieves a projection error of 1.760.08 pixels and a length deviation of 2.930.15\%, with a frame rate of 39.31.5 frames per second (FPS). These advancements have the potential to optimize robotic performance and increase the precision of complex endovascular interventions, ultimately contributing to better clinical outcomes. </t>
+  </si>
+  <si>
+    <t>Exploring the Design Space of 3D MLLMs for CT Report Generation</t>
+  </si>
+  <si>
+    <t>Multimodal Large Language Models (MLLMs) have emerged as a promising way to automate Radiology Report Generation (RRG). In this work, we systematically investigate the design space of 3D MLLMs, including visual input representation, projectors, Large Language Models (LLMs), and fine-tuning techniques for 3D CT report generation. We also introduce two knowledge-based report augmentation methods that improve performance on the GREEN score by up to 10\%, achieving the 2nd place on the MICCAI 2024 AMOS-MM challenge. Our results on the 1,687 cases from the AMOS-MM dataset show that RRG is largely independent of the size of LLM under the same training protocol. We also show that larger volume size does not always improve performance if the original ViT was pre-trained on a smaller volume size. Lastly, we show that using a segmentation mask along with the CT volume improves performance. The code is publicly available at https://github.com/bowang-lab/AMOS-MM-Solution</t>
+  </si>
+  <si>
+    <t>Lightweight Physics-Informed Zero-Shot Ultrasound Plane Wave Denoising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound Coherent Plane Wave Compounding (CPWC) enhances image contrast by combining echoes from multiple steered transmissions. While increasing the number of angles generally improves image quality, it drastically reduces the frame rate and can introduce blurring artifacts in fast-moving targets. Moreover, compounded images remain susceptible to noise, particularly when acquired with a limited number of transmissions. We propose a zero-shot denoising framework tailored for low-angle CPWC acquisitions, which enhances contrast without relying on a separate training dataset. The method divides the available transmission angles into two disjoint subsets, each used to form compound images that include higher noise levels. The new compounded images are then used to train a deep model via a self-supervised residual learning scheme, enabling it to suppress incoherent noise while preserving anatomical structures. Because angle-dependent artifacts vary between the subsets while the underlying tissue response is similar, this physics-informed pairing allows the network to learn to disentangle the inconsistent artifacts from the consistent tissue signal. Unlike supervised methods, our model requires no domain-specific fine-tuning or paired data, making it adaptable across anatomical regions and acquisition setups. The entire pipeline supports efficient training with low computational cost due to the use of a lightweight architecture, which comprises only two convolutional layers. Evaluations on simulation, phantom, and in vivo data demonstrate superior contrast enhancement and structure preservation compared to both classical and deep learning-based denoising methods. </t>
+  </si>
+  <si>
+    <t>SmoothSinger: A Conditional Diffusion Model for Singing Voice Synthesis with Multi-Resolution Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singing voice synthesis (SVS) aims to generate expressive and high-quality vocals from musical scores, requiring precise modeling of pitch, duration, and articulation. While diffusion-based models have achieved remarkable success in image and video generation, their application to SVS remains challenging due to the complex acoustic and musical characteristics of singing, often resulting in artifacts that degrade naturalness. In this work, we propose SmoothSinger, a conditional diffusion model designed to synthesize high quality and natural singing voices. Unlike prior methods that depend on vocoders as a final stage and often introduce distortion, SmoothSinger refines low-quality synthesized audio directly in a unified framework, mitigating the degradation associated with two-stage pipelines. The model adopts a reference-guided dual-branch architecture, using low-quality audio from any baseline system as a reference to guide the denoising process, enabling more expressive and context-aware synthesis. Furthermore, it enhances the conventional U-Net with a parallel low-frequency upsampling path, allowing the model to better capture pitch contours and long term spectral dependencies. To improve alignment during training, we replace reference audio with degraded ground truth audio, addressing temporal mismatch between reference and target signals. Experiments on the Opencpop dataset, a large-scale Chinese singing corpus, demonstrate that SmoothSinger achieves state-of-the-art results in both objective and subjective evaluations. Extensive ablation studies confirm its effectiveness in reducing artifacts and improving the naturalness of synthesized voices. </t>
+  </si>
+  <si>
+    <t>Spatial Mental Modeling from Limited Views</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Can Vision Language Models (VLMs) imagine the full scene from just a few views, like humans do? Humans form spatial mental models, internal representations of unseen space, to reason about layout, perspective, and motion. Our new MindCube benchmark with 21,154 questions across 3,268 images exposes this critical gap, where existing VLMs exhibit near-random performance. Using MindCube, we systematically evaluate how well VLMs build robust spatial mental models through representing positions (cognitive mapping), orientations (perspective-taking), and dynamics (mental simulation for "what-if" movements). We then explore three approaches to help VLMs approximate spatial mental models, including unseen intermediate views, natural language reasoning chains, and cognitive maps. The significant improvement comes from a synergistic approach, "map-then-reason", that jointly trains the model to first generate a cognitive map and then reason upon it. By training models to reason over these internal maps, we boosted accuracy from 37.8% to 60.8% (+23.0%). Adding reinforcement learning pushed performance even further to 70.7% (+32.9%). Our key insight is that such scaffolding of spatial mental models, actively constructing and utilizing internal structured spatial representations with flexible reasoning processes, significantly improves understanding of unobservable space. </t>
+  </si>
+  <si>
+    <t>FastRef:Fast Prototype Refinement for Few-Shot Industrial Anomaly Detection
+Authors: Long Tian, Yufei Li, Yuyang Dai, Wenchao Chen, Xiyang Liu, Bo Chen</t>
+  </si>
+  <si>
+    <t>Few-shot industrial anomaly detection (FS-IAD) presents a critical challenge for practical automated inspection systems operating in data-scarce environments. While existing approaches predominantly focus on deriving prototypes from limited normal samples, they typically neglect to systematically incorporate query image statistics to enhance prototype representativeness. To address this issue, we propose FastRef, a novel and efficient prototype refinement framework for FS-IAD. Our method operates through an iterative two-stage process: (1) characteristic transfer from query features to prototypes via an optimizable transformation matrix, and (2) anomaly suppression through prototype alignment. The characteristic transfer is achieved through linear reconstruction of query features from prototypes, while the anomaly suppression addresses a key observation in FS-IAD that unlike conventional IAD with abundant normal prototypes, the limited-sample setting makes anomaly reconstruction more probable. Therefore, we employ optimal transport (OT) for non-Gaussian sampled features to measure and minimize the gap between prototypes and their refined counterparts for anomaly suppression. For comprehensive evaluation, we integrate FastRef with three competitive prototype-based FS-IAD methods: PatchCore, FastRecon, WinCLIP, and AnomalyDINO. Extensive experiments across four benchmark datasets of MVTec, ViSA, MPDD and RealIAD demonstrate both the effectiveness and computational efficiency of our approach under 1/2/4-shots.</t>
+  </si>
+  <si>
+    <t>GenFlow: Interactive Modular System for Image Generation</t>
+  </si>
+  <si>
+    <t>Generative art unlocks boundless creative possibilities, yet its full potential remains untapped due to the technical expertise required for advanced architectural concepts and computational workflows. To bridge this gap, we present GenFlow, a novel modular framework that empowers users of all skill levels to generate images with precision and ease. Featuring a node-based editor for seamless customization and an intelligent assistant powered by natural language processing, GenFlow transforms the complexity of workflow creation into an intuitive and accessible experience. By automating deployment processes and minimizing technical barriers, our framework makes cutting-edge generative art tools available to everyone. A user study demonstrated GenFlow's ability to optimize workflows, reduce task completion times, and enhance user understanding through its intuitive interface and adaptive features. These results position GenFlow as a groundbreaking solution that redefines accessibility and efficiency in the realm of generative art.</t>
+  </si>
+  <si>
+    <t>Generalizable Neural Electromagnetic Inverse Scattering</t>
+  </si>
+  <si>
+    <t>Solving Electromagnetic Inverse Scattering Problems (EISP) is fundamental in applications such as medical imaging, where the goal is to reconstruct the relative permittivity from scattered electromagnetic field. This inverse process is inherently ill-posed and highly nonlinear, making it particularly challenging. A recent machine learning-based approach, Img-Interiors, shows promising results by leveraging continuous implicit functions. However, it requires case-specific optimization, lacks generalization to unseen data, and fails under sparse transmitter setups (e.g., with only one transmitter). To address these limitations, we revisit EISP from a physics-informed perspective, reformulating it as a two stage inverse transmission-scattering process. This formulation reveals the induced current as a generalizable intermediate representation, effectively decoupling the nonlinear scattering process from the ill-posed inverse problem. Built on this insight, we propose the first generalizable physics-driven framework for EISP, comprising a current estimator and a permittivity solver, working in an end-to-end manner. The current estimator explicitly learns the induced current as a physical bridge between the incident and scattered field, while the permittivity solver computes the relative permittivity directly from the estimated induced current. This design enables data-driven training and generalizable feed-forward prediction of relative permittivity on unseen data while maintaining strong robustness to transmitter sparsity. Extensive experiments show that our method outperforms state-of-the-art approaches in reconstruction accuracy, generalization, and robustness. This work offers a fundamentally new perspective on electromagnetic inverse scattering and represents a major step toward cost-effective practical solutions for electromagnetic imaging.</t>
+  </si>
+  <si>
+    <t>PanSt3R: Multi-view Consistent Panoptic Segmentation</t>
+  </si>
+  <si>
+    <t>Panoptic segmentation of 3D scenes, involving the segmentation and classification of object instances in a dense 3D reconstruction of a scene, is a challenging problem, especially when relying solely on unposed 2D images. Existing approaches typically leverage off-the-shelf models to extract per-frame 2D panoptic segmentations, before optimizing an implicit geometric representation (often based on NeRF) to integrate and fuse the 2D predictions. We argue that relying on 2D panoptic segmentation for a problem inherently 3D and multi-view is likely suboptimal as it fails to leverage the full potential of spatial relationships across views. In addition to requiring camera parameters, these approaches also necessitate computationally expensive test-time optimization for each scene. Instead, in this work, we propose a unified and integrated approach PanSt3R, which eliminates the need for test-time optimization by jointly predicting 3D geometry and multi-view panoptic segmentation in a single forward pass. Our approach builds upon recent advances in 3D reconstruction, specifically upon MUSt3R, a scalable multi-view version of DUSt3R, and enhances it with semantic awareness and multi-view panoptic segmentation capabilities. We additionally revisit the standard post-processing mask merging procedure and introduce a more principled approach for multi-view segmentation. We also introduce a simple method for generating novel-view predictions based on the predictions of PanSt3R and vanilla 3DGS. Overall, the proposed PanSt3R is conceptually simple, yet fast and scalable, and achieves state-of-the-art performance on several benchmarks, while being orders of magnitude faster than existing methods.</t>
+  </si>
+  <si>
+    <t>GANet-Seg: Adversarial Learning for Brain Tumor Segmentation with Hybrid Generative Models</t>
+  </si>
+  <si>
+    <t>This work introduces a novel framework for brain tumor segmentation leveraging pre-trained GANs and Unet architectures. By combining a global anomaly detection module with a refined mask generation network, the proposed model accurately identifies tumor-sensitive regions and iteratively enhances segmentation precision using adversarial loss constraints. Multi-modal MRI data and synthetic image augmentation are employed to improve robustness and address the challenge of limited annotated datasets. Experimental results on the BraTS dataset demonstrate the effectiveness of the approach, achieving high sensitivity and accuracy in both lesion-wise Dice and HD95 metrics than the baseline. This scalable method minimizes the dependency on fully annotated data, paving the way for practical real-world applications in clinical settings.</t>
+  </si>
+  <si>
+    <t>ReME: A Data-Centric Framework for Training-Free Open-Vocabulary Segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training-free open-vocabulary semantic segmentation (OVS) aims to segment images given a set of arbitrary textual categories without costly model fine-tuning. Existing solutions often explore attention mechanisms of pre-trained models, such as CLIP, or generate synthetic data and design complex retrieval processes to perform OVS. However, their performance is limited by the capability of reliant models or the suboptimal quality of reference sets. In this work, we investigate the largely overlooked data quality problem for this challenging dense scene understanding task, and identify that a high-quality reference set can significantly benefit training-free OVS. With this observation, we introduce a data-quality-oriented framework, comprising a data pipeline to construct a reference set with well-paired segment-text embeddings and a simple similarity-based retrieval to unveil the essential effect of data. Remarkably, extensive evaluations on ten benchmark datasets demonstrate that our method outperforms all existing training-free OVS approaches, highlighting the importance of data-centric design for advancing OVS without training. Our code is available at https://github.com/xiweix/ReME . </t>
+  </si>
+  <si>
+    <t>BitMark for Infinity: Watermarking Bitwise Autoregressive Image Generative Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> State-of-the-art text-to-image models like Infinity generate photorealistic images at an unprecedented speed. These models operate in a bitwise autoregressive manner over a discrete set of tokens that is practically infinite in size. However, their impressive generative power comes with a growing risk: as their outputs increasingly populate the Internet, they are likely to be scraped and reused as training data-potentially by the very same models. This phenomenon has been shown to lead to model collapse, where repeated training on generated content, especially from the models' own previous versions, causes a gradual degradation in performance. A promising mitigation strategy is watermarking, which embeds human-imperceptible yet detectable signals into generated images-enabling the identification of generated content. In this work, we introduce BitMark, a robust bitwise watermarking framework for Infinity. Our method embeds a watermark directly at the bit level of the token stream across multiple scales (also referred to as resolutions) during Infinity's image generation process. Our bitwise watermark subtly influences the bits to preserve visual fidelity and generation speed while remaining robust against a spectrum of removal techniques. Furthermore, it exhibits high radioactivity, i.e., when watermarked generated images are used to train another image generative model, this second model's outputs will also carry the watermark. The radioactive traces remain detectable even when only fine-tuning diffusion or image autoregressive models on images watermarked with our BitMark. Overall, our approach provides a principled step toward preventing model collapse in image generative models by enabling reliable detection of generated outputs</t>
+  </si>
+  <si>
+    <t>MedPrompt: LLM-CNN Fusion with Weight Routing for Medical Image Segmentation and Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current medical image analysis systems are typically task-specific, requiring separate models for classification and segmentation, and lack the flexibility to support user-defined workflows. To address these challenges, we introduce MedPrompt, a unified framework that combines a few-shot prompted Large Language Model (Llama-4-17B) for high-level task planning with a modular Convolutional Neural Network (DeepFusionLab) for low-level image processing. The LLM interprets user instructions and generates structured output to dynamically route task-specific pretrained weights. This weight routing approach avoids retraining the entire framework when adding new tasks-only task-specific weights are required, enhancing scalability and deployment. We evaluated MedPrompt across 19 public datasets, covering 12 tasks spanning 5 imaging modalities. The system achieves a 97% end-to-end correctness in interpreting and executing prompt-driven instructions, with an average inference latency of 2.5 seconds, making it suitable for near real-time applications. DeepFusionLab achieves competitive segmentation accuracy (e.g., Dice 0.9856 on lungs) and strong classification performance (F1 0.9744 on tuberculosis). Overall, MedPrompt enables scalable, prompt-driven medical imaging by combining the interpretability of LLMs with the efficiency of modular CNNs. </t>
+  </si>
+  <si>
+    <t>Unlocking Constraints: Source-Free Occlusion-Aware Seamless Segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Panoramic image processing is essential for omni-context perception, yet faces constraints like distortions, perspective occlusions, and limited annotations. Previous unsupervised domain adaptation methods transfer knowledge from labeled pinhole data to unlabeled panoramic images, but they require access to source pinhole data. To address these, we introduce a more practical task, i.e., Source-Free Occlusion-Aware Seamless Segmentation (SFOASS), and propose its first solution, called UNconstrained Learning Omni-Context Knowledge (UNLOCK). Specifically, UNLOCK includes two key modules: Omni Pseudo-Labeling Learning and Amodal-Driven Context Learning. While adapting without relying on source data or target labels, this framework enhances models to achieve segmentation with 360° viewpoint coverage and occlusion-aware reasoning. Furthermore, we benchmark the proposed SFOASS task through both real-to-real and synthetic-to-real adaptation settings. Experimental results show that our source-free method achieves performance comparable to source-dependent methods, yielding state-of-the-art scores of 10.9 in mAAP and 11.6 in mAP, along with an absolute improvement of +4.3 in mAPQ over the source-only method. All data and code will be made publicly available at https://github.com/yihong-97/UNLOCK.</t>
+  </si>
+  <si>
+    <t>Out-of-Distribution Semantic Occupancy Prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D Semantic Occupancy Prediction is crucial for autonomous driving, providing a dense, semantically rich environmental representation. However, existing methods focus on in-distribution scenes, making them susceptible to Out-of-Distribution (OoD) objects and long-tail distributions, which increases the risk of undetected anomalies and misinterpretations, posing safety hazards. To address these challenges, we introduce Out-of-Distribution Semantic Occupancy Prediction, targeting OoD detection in 3D voxel space. To fill the gaps in the dataset, we propose a Synthetic Anomaly Integration Pipeline that injects synthetic anomalies while preserving realistic spatial and occlusion patterns, enabling the creation of two datasets: VAA-KITTI and VAA-KITTI-360. We introduce OccOoD, a novel framework integrating OoD detection into 3D semantic occupancy prediction, with Voxel-BEV Progressive Fusion (VBPF) leveraging an RWKV-based branch to enhance OoD detection via geometry-semantic fusion. Experimental results demonstrate that OccOoD achieves state-of-the-art OoD detection with an AuROC of 67.34% and an AuPRCr of 29.21% within a 1.2m region, while maintaining competitive occupancy prediction performance. The established datasets and source code will be made publicly available at https://github.com/7uHeng/OccOoD. </t>
+  </si>
+  <si>
+    <t>Uncover Treasures in DCT: Advancing JPEG Quality Enhancement by Exploiting Latent Correlations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint Photographic Experts Group (JPEG) achieves data compression by quantizing Discrete Cosine Transform (DCT) coefficients, which inevitably introduces compression artifacts. Most existing JPEG quality enhancement methods operate in the pixel domain, suffering from the high computational costs of decoding. Consequently, direct enhancement of JPEG images in the DCT domain has gained increasing attention. However, current DCT-domain methods often exhibit limited performance. To address this challenge, we identify two critical types of correlations within the DCT coefficients of JPEG images. Building on this insight, we propose an Advanced DCT-domain JPEG Quality Enhancement (AJQE) method that fully exploits these correlations. The AJQE method enables the adaptation of numerous well-established pixel-domain models to the DCT domain, achieving superior performance with reduced computational complexity. Compared to the pixel-domain counterparts, the DCT-domain models derived by our method demonstrate a 0.35 dB improvement in PSNR and a 60.5% increase in enhancement throughput on average. </t>
+  </si>
+  <si>
+    <t>https://arxiv.org/search/?query=image+processing&amp;searchtype=all&amp;abstracts=show&amp;order=-announced_date_first&amp;size=50&amp;start=50</t>
+  </si>
+  <si>
+    <t>MVGBench: Comprehensive Benchmark for Multi-view Generation Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We propose MVGBench, a comprehensive benchmark for multi-view image generation models (MVGs) that evaluates 3D consistency in geometry and texture, image quality, and semantics (using vision language models). Recently, MVGs have been the main driving force in 3D object creation. However, existing metrics compare generated images against ground truth target views, which is not suitable for generative tasks where multiple solutions exist while differing from ground truth. Furthermore, different MVGs are trained on different view angles, synthetic data and specific lightings -- robustness to these factors and generalization to real data are rarely evaluated thoroughly. Without a rigorous evaluation protocol, it is also unclear what design choices contribute to the progress of MVGs. MVGBench evaluates three different aspects: best setup performance, generalization to real data and robustness. Instead of comparing against ground truth, we introduce a novel 3D self-consistency metric which compares 3D reconstructions from disjoint generated multi-views. We systematically compare 12 existing MVGs on 4 different curated real and synthetic datasets. With our analysis, we identify important limitations of existing methods specially in terms of robustness and generalization, and we find the most critical design choices. Using the discovered best practices, we propose ViFiGen, a method that outperforms all evaluated MVGs on 3D consistency. Our code, model, and benchmark suite will be publicly released. </t>
+  </si>
+  <si>
+    <t>Calligrapher: Freestyle Text Image Customization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We introduce Calligrapher, a novel diffusion-based framework that innovatively integrates advanced text customization with artistic typography for digital calligraphy and design applications. Addressing the challenges of precise style control and data dependency in typographic customization, our framework incorporates three key technical contributions. First, we develop a self-distillation mechanism that leverages the pre-trained text-to-image generative model itself alongside the large language model to automatically construct a style-centric typography benchmark. Second, we introduce a localized style injection framework via a trainable style encoder, which comprises both Qformer and linear layers, to extract robust style features from reference images. An in-context generation mechanism is also employed to directly embed reference images into the denoising process, further enhancing the refined alignment of target styles. Extensive quantitative and qualitative evaluations across diverse fonts and design contexts confirm Calligrapher's accurate reproduction of intricate stylistic details and precise glyph positioning. By automating high-quality, visually consistent typography, Calligrapher surpasses traditional models, empowering creative practitioners in digital art, branding, and contextual typographic design. </t>
+  </si>
+  <si>
+    <t>Navigating with Annealing Guidance Scale in Diffusion Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Denoising diffusion models excel at generating high-quality images conditioned on text prompts, yet their effectiveness heavily relies on careful guidance during the sampling process. Classifier-Free Guidance (CFG) provides a widely used mechanism for steering generation by setting the guidance scale, which balances image quality and prompt alignment. However, the choice of the guidance scale has a critical impact on the convergence toward a visually appealing and prompt-adherent image. In this work, we propose an annealing guidance scheduler which dynamically adjusts the guidance scale over time based on the conditional noisy signal. By learning a scheduling policy, our method addresses the temperamental behavior of CFG. Empirical results demonstrate that our guidance scheduler significantly enhances image quality and alignment with the text prompt, advancing the performance of text-to-image generation. Notably, our novel scheduler requires no additional activations or memory consumption, and can seamlessly replace the common classifier-free guidance, offering an improved trade-off between prompt alignment and quality. </t>
+  </si>
+  <si>
+    <t>DenseWorld-1M: Towards Detailed Dense Grounded Caption in the Real World</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multimodal Large Language Models (MLLMs) demonstrate a complex understanding of scenes, benefiting from large-scale and high-quality datasets. Most existing caption datasets lack the ground locations and relations for visual entities. Several grounded caption datasets face the problems of missing detailed descriptions, relations, and massive object descriptions on high-resolution images. To fill this gap for the community, we present DenseWorld-1M, the first massive, detailed, dense grounded caption dataset in the real world. We design a three-stage labeling pipeline, containing open-world perception, detailed object caption generation, and dense caption merging. The first stage obtains entity-level masks and labels. The second stage generates the object-level, detailed captions with the guidance of masks and labels from the first stage. The final stage merges object captions and masks into spatial and relational dense captions. To accelerate the labeling process and improve caption quality, we present two VLM models: the Detailed Region Caption model and the Spatial Caption Merging model. Extensive experiments on various settings, including vision-language understanding, visual grounding, and region caption generation, demonstrate the effectiveness of our DenseWorld-1M dataset and labeling models. </t>
+  </si>
+  <si>
+    <t>MILo: Mesh-In-the-Loop Gaussian Splatting for Detailed and Efficient Surface Reconstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While recent advances in Gaussian Splatting have enabled fast reconstruction of high-quality 3D scenes from images, extracting accurate surface meshes remains a challenge. Current approaches extract the surface through costly post-processing steps, resulting in the loss of fine geometric details or requiring significant time and leading to very dense meshes with millions of vertices. More fundamentally, the a posteriori conversion from a volumetric to a surface representation limits the ability of the final mesh to preserve all geometric structures captured during training. We present MILo, a novel Gaussian Splatting framework that bridges the gap between volumetric and surface representations by differentiably extracting a mesh from the 3D Gaussians. We design a fully differentiable procedure that constructs the mesh-including both vertex locations and connectivity-at every iteration directly from the parameters of the Gaussians, which are the only quantities optimized during training. Our method introduces three key technical contributions: a bidirectional consistency framework ensuring both representations-Gaussians and the extracted mesh-capture the same underlying geometry during training; an adaptive mesh extraction process performed at each training iteration, which uses Gaussians as differentiable pivots for Delaunay triangulation; a novel method for computing signed distance values from the 3D Gaussians that enables precise surface extraction while avoiding geometric erosion. Our approach can reconstruct complete scenes, including backgrounds, with state-of-the-art quality while requiring an order of magnitude fewer mesh vertices than previous methods. Due to their light weight and empty interior, our meshes are well suited for downstream applications such as physics simulations or animation. </t>
+  </si>
+  <si>
+    <t>WaRA: Wavelet Low Rank Adaptation</t>
+  </si>
+  <si>
+    <t>Parameter-efficient fine-tuning (PEFT) has gained widespread adoption across various applications. Among PEFT techniques, Low-Rank Adaptation (LoRA) and its extensions have emerged as particularly effective, allowing efficient model adaptation while significantly reducing computational overhead. However, existing approaches typically rely on global low-rank factorizations, which overlook local or multi-scale structure, failing to capture complex patterns in the weight updates. To address this, we propose WaRA, a novel PEFT method that leverages wavelet transforms to decompose the weight update matrix into a multi-resolution representation. By performing low-rank factorization in the wavelet domain and reconstructing updates through an inverse transform, WaRA obtains compressed adaptation parameters that harness multi-resolution analysis, enabling it to capture both coarse and fine-grained features while providing greater flexibility and sparser representations than standard LoRA. Through comprehensive experiments and analysis, we demonstrate that WaRA performs superior on diverse vision tasks, including image generation, classification, and semantic segmentation, significantly enhancing generated image quality while reducing computational complexity. Although WaRA was primarily designed for vision tasks, we further showcase its effectiveness in language tasks, highlighting its broader applicability and generalizability. The code is publicly available at \href{GitHub}{https://github.com/moeinheidari7829/WaRA}</t>
+  </si>
+  <si>
+    <t>Imagine for Me: Creative Conceptual Blending of Real Images and Text via Blended Attention</t>
+  </si>
+  <si>
+    <t>Blending visual and textual concepts into a new visual concept is a unique and powerful trait of human beings that can fuel creativity. However, in practice, cross-modal conceptual blending for humans is prone to cognitive biases, like design fixation, which leads to local minima in the design space. In this paper, we propose a T2I diffusion adapter "IT-Blender" that can automate the blending process to enhance human creativity. Prior works related to cross-modal conceptual blending are limited in encoding a real image without loss of details or in disentangling the image and text inputs. To address these gaps, IT-Blender leverages pretrained diffusion models (SD and FLUX) to blend the latent representations of a clean reference image with those of the noisy generated image. Combined with our novel blended attention, IT-Blender encodes the real reference image without loss of details and blends the visual concept with the object specified by the text in a disentangled way. Our experiment results show that IT-Blender outperforms the baselines by a large margin in blending visual and textual concepts, shedding light on the new application of image generative models to augment human creativity.</t>
+  </si>
+  <si>
+    <t>C3VDv2 -- Colonoscopy 3D video dataset with enhanced realism</t>
+  </si>
+  <si>
+    <t>Computer vision techniques have the potential to improve the diagnostic performance of colonoscopy, but the lack of 3D colonoscopy datasets for training and validation hinders their development. This paper introduces C3VDv2, the second version (v2) of the high-definition Colonoscopy 3D Video Dataset, featuring enhanced realism designed to facilitate the quantitative evaluation of 3D colon reconstruction algorithms. 192 video sequences were captured by imaging 60 unique, high-fidelity silicone colon phantom segments. Ground truth depth, surface normals, optical flow, occlusion, six-degree-of-freedom pose, coverage maps, and 3D models are provided for 169 colonoscopy videos. Eight simulated screening colonoscopy videos acquired by a gastroenterologist are provided with ground truth poses. The dataset includes 15 videos featuring colon deformations for qualitative assessment. C3VDv2 emulates diverse and challenging scenarios for 3D reconstruction algorithms, including fecal debris, mucous pools, blood, debris obscuring the colonoscope lens, en-face views, and fast camera motion. The enhanced realism of C3VDv2 will allow for more robust and representative development and evaluation of 3D reconstruction algorithms.</t>
+  </si>
+  <si>
+    <t>Continual Adaptation: Environment-Conditional Parameter Generation for Object Detection in Dynamic Scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In practice, environments constantly change over time and space, posing significant challenges for object detectors trained based on a closed-set assumption, i.e., training and test data share the same distribution. To this end, continual test-time adaptation has attracted much attention, aiming to improve detectors' generalization by fine-tuning a few specific parameters, e.g., BatchNorm layers. However, based on a small number of test images, fine-tuning certain parameters may affect the representation ability of other fixed parameters, leading to performance degradation. Instead, we explore a new mechanism, i.e., converting the fine-tuning process to a specific-parameter generation. Particularly, we first design a dual-path LoRA-based domain-aware adapter that disentangles features into domain-invariant and domain-specific components, enabling efficient adaptation. Additionally, a conditional diffusion-based parameter generation mechanism is presented to synthesize the adapter's parameters based on the current environment, preventing the optimization from getting stuck in local optima. Finally, we propose a class-centered optimal transport alignment method to mitigate catastrophic forgetting. Extensive experiments conducted on various continuous domain adaptive object detection tasks demonstrate the effectiveness. Meanwhile, visualization results show that the representation extracted by the generated parameters can capture more object-related information and strengthen the generalization ability. </t>
+  </si>
+  <si>
+    <t>Simultaneous Super-Resolution of Spatial and Spectral Imaging with a Camera Array and Notch Filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This study proposes an algorithm based on a notch filter camera array system for simultaneous super-resolution imaging and spectral reconstruction, enhancing the spatial resolution and multispectral imaging capabilities of targets. In this study, multi-aperture super-resolution algorithms, pan-sharpening techniques, and spectral reconstruction algorithms were investigated and integrated. The sub-pixel level offset information and spectral disparities among the 9 low-resolution images captured by the 9 distinct imaging apertures were utilized, leading to the successful reconstruction of 31 super-resolution spectral images. By conducting simulations with a publicly available dataset and performing qualitative and quantitative comparisons with snapshot coded aperture spectral imaging systems, the experimental results demonstrate that our system and algorithm attained a peak signal-to-noise ratio of 35.6dB, representing a 5dB enhancement over the most advanced snapshot coded aperture spectral imaging systems, while also reducing processing time. This research offers an effective solution for achieving high temporal, spectral, and spatial resolution through the utilization of multi-aperture imaging systems</t>
+  </si>
+  <si>
+    <t>ShapeKit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this paper, we present a practical approach to improve anatomical shape accuracy in whole-body medical segmentation. Our analysis shows that a shape-focused toolkit can enhance segmentation performance by over 8%, without the need for model re-training or fine-tuning. In comparison, modifications to model architecture typically lead to marginal gains of less than 3%. Motivated by this observation, we introduce ShapeKit, a flexible and easy-to-integrate toolkit designed to refine anatomical shapes. This work highlights the underappreciated value of shape-based tools and calls attention to their potential impact within the medical segmentation community. </t>
+  </si>
+  <si>
+    <t>Harnessing AI Agents to Advance Research on Refugee Child Mental Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The international refugee crisis deepens, exposing millions of dis placed children to extreme psychological trauma. This research suggests a com pact, AI-based framework for processing unstructured refugee health data and distilling knowledge on child mental health. We compare two Retrieval-Aug mented Generation (RAG) pipelines, Zephyr-7B-beta and DeepSeek R1-7B, to determine how well they process challenging humanitarian datasets while avoid ing hallucination hazards. By combining cutting-edge AI methods with migration research and child psychology, this study presents a scalable strategy to assist policymakers, mental health practitioners, and humanitarian agencies to better assist displaced children and recognize their mental wellbeing. In total, both the models worked properly but significantly Deepseek R1 is superior to Zephyr with an accuracy of answer relevance 0.91 </t>
+  </si>
+  <si>
+    <t>Thinking with Images for Multimodal Reasoning: Foundations, Methods, and Future Frontiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent progress in multimodal reasoning has been significantly advanced by textual Chain-of-Thought (CoT), a paradigm where models conduct reasoning within language. This text-centric approach, however, treats vision as a static, initial context, creating a fundamental "semantic gap" between rich perceptual data and discrete symbolic thought. Human cognition often transcends language, utilizing vision as a dynamic mental sketchpad. A similar evolution is now unfolding in AI, marking a fundamental paradigm shift from models that merely think about images to those that can truly think with images. This emerging paradigm is characterized by models leveraging visual information as intermediate steps in their thought process, transforming vision from a passive input into a dynamic, manipulable cognitive workspace. In this survey, we chart this evolution of intelligence along a trajectory of increasing cognitive autonomy, which unfolds across three key stages: from external tool exploration, through programmatic manipulation, to intrinsic imagination. To structure this rapidly evolving field, our survey makes four key contributions. (1) We establish the foundational principles of the think with image paradigm and its three-stage framework. (2) We provide a comprehensive review of the core methods that characterize each stage of this roadmap. (3) We analyze the critical landscape of evaluation benchmarks and transformative applications. (4) We identify significant challenges and outline promising future directions. By providing this structured overview, we aim to offer a clear roadmap for future research towards more powerful and human-aligned multimodal AI. </t>
+  </si>
+  <si>
+    <t>Spatially Gene Expression Prediction using Dual-Scale Contrastive Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Spatial transcriptomics (ST) provides crucial insights into tissue micro-environments, but is limited to its high cost and complexity. As an alternative, predicting gene expression from pathology whole slide images (WSI) is gaining increasing attention. However, existing methods typically rely on single patches or a single pathology modality, neglecting the complex spatial and molecular interactions between target and neighboring information (e.g., gene co-expression). This leads to a failure in establishing connections among adjacent regions and capturing intricate cross-modal relationships. To address these issues, we propose NH2ST, a framework that integrates spatial context and both pathology and gene modalities for gene expression prediction. Our model comprises a query branch and a neighbor branch to process paired target patch and gene data and their neighboring regions, where cross-attention and contrastive learning are employed to capture intrinsic associations and ensure alignments between pathology and gene expression. Extensive experiments on six datasets demonstrate that our model consistently outperforms existing methods, achieving over 20% in PCC metrics. Codes are available at https://github.com/MCPathology/NH2ST </t>
+  </si>
+  <si>
+    <t>Flash-VStream: Efficient Real-Time Understanding for Long Video Streams</t>
+  </si>
+  <si>
+    <t>Benefiting from the advances in large language models and cross-modal alignment, existing multimodal large language models have achieved prominent performance in image and short video understanding. However, the understanding of long videos is still challenging, as their long-context nature results in significant computational and memory overhead. Most existing work treats long videos in the same way as short videos, which is inefficient for real-world applications and hard to generalize to even longer videos. To address these issues, we propose Flash-VStream, an efficient video language model capable of processing extremely long videos and responding to user queries in real time. Particularly, we design a Flash Memory module, containing a low-capacity context memory to aggregate long-context temporal information and model the distribution of information density, and a high-capacity augmentation memory to retrieve detailed spatial information based on this distribution. Compared to existing models, Flash-VStream achieves significant reductions in inference latency. Extensive experiments on long video benchmarks and comprehensive video benchmarks, i.e., EgoSchema, MLVU, LVBench, MVBench and Video-MME, demonstrate the state-of-the-art performance and outstanding efficiency of our method. Code is available at https://github.com/IVGSZ/Flash-VStream</t>
+  </si>
+  <si>
+    <t>Controllable Reference-Based Real-World Remote Sensing Image Super-Resolution with Generative Diffusion Priors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super-resolution (SR) techniques can enhance the spatial resolution of remote sensing images by utilizing low-resolution (LR) images to reconstruct high-resolution (HR) images, enabling more efficient large-scale earth observation applications. While single-image super-resolution (SISR) methods have shown progress, reference-based super-resolution (RefSR) offers superior performance by incorporating historical HR images alongside current LR observations. However, existing RefSR methods struggle with real-world complexities, such as cross-sensor resolution gap and significant land cover changes, often leading to under-generation or over-reliance on reference image. To address these challenges, we propose CRefDiff, a novel controllable reference-based diffusion model for real-world remote sensing image SR. To address the under-generation problem, CRefDiff is built upon the pretrained Stable Diffusion model, leveraging its powerful generative prior to produce accurate structures and textures. To mitigate over-reliance on the reference, we introduce a dual-branch fusion mechanism that adaptively integrates both local and global information from the reference image. Moreover, this novel dual-branch design enables reference strength control during inference, enhancing interactivity and flexibility of the model. Finally, a strategy named Better Start is proposed to significantly reduce the number of denoising steps, thereby accelerating the inference process. To support further research, we introduce Real-RefRSSRD, a new real-world RefSR dataset for remote sensing images, consisting of HR NAIP and LR Sentinel-2 image pairs with diverse land cover changes and significant temporal gaps. Extensive experiments on Real-RefRSSRD show that CRefDiff achieves state-of-the-art performance across various metrics and improves downstream tasks such as scene classification and semantic segmentation. </t>
+  </si>
+  <si>
+    <t>Towards the Training of Deeper Predictive Coding Neural Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictive coding networks trained with equilibrium propagation are neural models that perform inference through an iterative energy minimization process. Previous studies have demonstrated their effectiveness in shallow architectures, but show significant performance degradation when depth exceeds five to seven layers. In this work, we show that the reason behind this degradation is due to exponentially imbalanced errors between layers during weight updates, and predictions from the previous layer not being effective in guiding updates in deeper layers. We address the first issue by introducing two novel methods to optimize the latent variables that use precision-weighting to re-balance the distribution of energy among layers during the `relaxation phase', and the second issue by proposing a novel weight update mechanism that reduces error accumulation in deeper layers. Empirically, we test our methods on a large number of image classification tasks, resulting in large improvements in test accuracy across networks with more than seven layers, with performances comparable to those of backprop on similar models. These findings suggest that a better understanding of the relaxation phase is important to train models using equilibrium propagation at scale, and open new possibilities for their application in complex tasks. </t>
+  </si>
+  <si>
+    <t>Visual Textualization for Image Prompted Object Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We propose VisTex-OVLM, a novel image prompted object detection method that introduces visual textualization -- a process that projects a few visual exemplars into the text feature space to enhance Object-level Vision-Language Models' (OVLMs) capability in detecting rare categories that are difficult to describe textually and nearly absent from their pre-training data, while preserving their pre-trained object-text alignment. Specifically, VisTex-OVLM leverages multi-scale textualizing blocks and a multi-stage fusion strategy to integrate visual information from visual exemplars, generating textualized visual tokens that effectively guide OVLMs alongside text prompts. Unlike previous methods, our method maintains the original architecture of OVLM, maintaining its generalization capabilities while enhancing performance in few-shot settings. VisTex-OVLM demonstrates superior performance across open-set datasets which have minimal overlap with OVLM's pre-training data and achieves state-of-the-art results on few-shot benchmarks PASCAL VOC and MSCOCO. The code will be released at https://github.com/WitGotFlg/VisTex-OVLM. </t>
+  </si>
+  <si>
+    <t>Spatio-Temporal Representation Decoupling and Enhancement for Federated Instrument Segmentation in Surgical Videos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Surgical instrument segmentation under Federated Learning (FL) is a promising direction, which enables multiple surgical sites to collaboratively train the model without centralizing datasets. However, there exist very limited FL works in surgical data science, and FL methods for other modalities do not consider inherent characteristics in surgical domain: i) different scenarios show diverse anatomical backgrounds while highly similar instrument representation; ii) there exist surgical simulators which promote large-scale synthetic data generation with minimal efforts. In this paper, we propose a novel Personalized FL scheme, Spatio-Temporal Representation Decoupling and Enhancement (FedST), which wisely leverages surgical domain knowledge during both local-site and global-server training to boost segmentation. Concretely, our model embraces a Representation Separation and Cooperation (RSC) mechanism in local-site training, which decouples the query embedding layer to be trained privately, to encode respective backgrounds. Meanwhile, other parameters are optimized globally to capture the consistent representations of instruments, including the temporal layer to capture similar motion patterns. A textual-guided channel selection is further designed to highlight site-specific features, facilitating model adapta tion to each site. Moreover, in global-server training, we propose Synthesis-based Explicit Representation Quantification (SERQ), which defines an explicit representation target based on synthetic data to synchronize the model convergence during fusion for improving model generalization.</t>
+  </si>
+  <si>
+    <t>Radioactive Watermarks in Diffusion and Autoregressive Image Generative Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Image generative models have become increasingly popular, but training them requires large datasets that are costly to collect and curate. To circumvent these costs, some parties may exploit existing models by using the generated images as training data for their own models. In general, watermarking is a valuable tool for detecting unauthorized use of generated images. However, when these images are used to train a new model, watermarking can only enable detection if the watermark persists through training and remains identifiable in the outputs of the newly trained model - a property known as radioactivity. We analyze the radioactivity of watermarks in images generated by diffusion models (DMs) and image autoregressive models (IARs). We find that existing watermarking methods for DMs fail to retain radioactivity, as watermarks are either erased during encoding into the latent space or lost in the noising-denoising process (during the training in the latent space). Meanwhile, despite IARs having recently surpassed DMs in image generation quality and efficiency, no radioactive watermarking methods have been proposed for them. To overcome this limitation, we propose the first watermarking method tailored for IARs and with radioactivity in mind - drawing inspiration from techniques in large language models (LLMs), which share IARs' autoregressive paradigm. Our extensive experimental evaluation highlights our method's effectiveness in preserving radioactivity within IARs, enabling robust provenance tracking, and preventing unauthorized use of their generated images. </t>
+  </si>
+  <si>
+    <t>Deep Learning-Based Semantic Segmentation for Real-Time Kidney Imaging and Measurements with Augmented Reality-Assisted Ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound (US) is widely accessible and radiation-free but has a steep learning curve due to its dynamic nature and non-standard imaging planes. Additionally, the constant need to shift focus between the US screen and the patient poses a challenge. To address these issues, we integrate deep learning (DL)-based semantic segmentation for real-time (RT) automated kidney volumetric measurements, which are essential for clinical assessment but are traditionally time-consuming and prone to fatigue. This automation allows clinicians to concentrate on image interpretation rather than manual measurements. Complementing DL, augmented reality (AR) enhances the usability of US by projecting the display directly into the clinician's field of view, improving ergonomics and reducing the cognitive load associated with screen-to-patient transitions. Two AR-DL-assisted US pipelines on HoloLens-2 are proposed: one streams directly via the application programming interface for a wireless setup, while the other supports any US device with video output for broader accessibility. We evaluate RT feasibility and accuracy using the Open Kidney Dataset and open-source segmentation models (nnU-Net, Segmenter, YOLO with MedSAM and LiteMedSAM). Our open-source GitHub pipeline includes model implementations, measurement algorithms, and a Wi-Fi-based streaming solution, enhancing US training and diagnostics, especially in point-of-care settings. </t>
+  </si>
+  <si>
+    <t>Subjective Camera: Bridging Human Cognition and Visual Reconstruction through Sequence-Aware Sketch-Guided Diffusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We propose Subjective Camera, a human-as-imaging-device paradigm that reconstructs real-world scenes from mental impressions through synergistic use of verbal descriptions and progressive rough sketches. This approach overcomes dual limitations of language ambiguity and sketch abstraction by treating the user's drawing sequence as priors, effectively translating subjective perceptual expectations into photorealistic images. Existing approaches face three fundamental barriers: (1) user-specific subjective input biases, (2) huge modality gap between planar sketch and 3D priors in diffusion, and (3) sketch quality-sensitive performance degradation. Current solutions either demand resource-intensive model adaptation or impose impractical requirements on sketch precision. Our framework addresses these challenges through concept-sequential generation. (1) We establish robust appearance priors through text-reward optimization, and then implement sequence-aware disentangled generation that processes concepts in sketching order; these steps accommodate user-specific subjective expectation in a train-free way. (2) We employ latent optimization that effectively bridges the modality gap between planar sketches and 3D priors in diffusion. (3) Our hierarchical reward-guided framework enables the use of rough sketches without demanding artistic expertise. Comprehensive evaluation across diverse datasets demonstrates that our approach achieves state-of-the-art performance in maintaining both semantic and spatial coherence. </t>
+  </si>
+  <si>
+    <t>MDPG: Multi-domain Diffusion Prior Guidance for MRI Reconstruction</t>
+  </si>
+  <si>
+    <t>Magnetic Resonance Imaging (MRI) reconstruction is essential in medical diagnostics. As the latest generative models, diffusion models (DMs) have struggled to produce high-fidelity images due to their stochastic nature in image domains. Latent diffusion models (LDMs) yield both compact and detailed prior knowledge in latent domains, which could effectively guide the model towards more effective learning of the original data distribution. Inspired by this, we propose Multi-domain Diffusion Prior Guidance (MDPG) provided by pre-trained LDMs to enhance data consistency in MRI reconstruction tasks. Specifically, we first construct a Visual-Mamba-based backbone, which enables efficient encoding and reconstruction of under-sampled images. Then pre-trained LDMs are integrated to provide conditional priors in both latent and image domains. A novel Latent Guided Attention (LGA) is proposed for efficient fusion in multi-level latent domains. Simultaneously, to effectively utilize a prior in both the k-space and image domain, under-sampled images are fused with generated full-sampled images by the Dual-domain Fusion Branch (DFB) for self-adaption guidance. Lastly, to further enhance the data consistency, we propose a k-space regularization strategy based on the non-auto-calibration signal (NACS) set. Extensive experiments on two public MRI datasets fully demonstrate the effectiveness of the proposed methodology. The code is available at https://github.com/Zolento/MDPG.</t>
+  </si>
+  <si>
+    <t>MedSAM-CA: A CNN-Augmented ViT with Attention-Enhanced Multi-Scale Fusion for Medical Image Segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical image segmentation plays a crucial role in clinical diagnosis and treatment planning, where accurate boundary delineation is essential for precise lesion localization, organ identification, and quantitative assessment. In recent years, deep learning-based methods have significantly advanced segmentation accuracy. However, two major challenges remain. First, the performance of these methods heavily relies on large-scale annotated datasets, which are often difficult to obtain in medical scenarios due to privacy concerns and high annotation costs. Second, clinically challenging scenarios, such as low contrast in certain imaging modalities and blurry lesion boundaries caused by malignancy, still pose obstacles to precise segmentation. To address these challenges, we propose MedSAM-CA, an architecture-level fine-tuning approach that mitigates reliance on extensive manual annotations by adapting the pretrained foundation model, Medical Segment Anything (MedSAM). MedSAM-CA introduces two key components: the Convolutional Attention-Enhanced Boundary Refinement Network (CBR-Net) and the Attention-Enhanced Feature Fusion Block (Atte-FFB). CBR-Net operates in parallel with the MedSAM encoder to recover boundary information potentially overlooked by long-range attention mechanisms, leveraging hierarchical convolutional processing. Atte-FFB, embedded in the MedSAM decoder, fuses multi-level fine-grained features from skip connections in CBR-Net with global representations upsampled within the decoder to enhance boundary delineation accuracy. Experiments on publicly available datasets covering dermoscopy, CT, and MRI imaging modalities validate the effectiveness of MedSAM-CA. On dermoscopy dataset, MedSAM-CA achieves 94.43% Dice with only 2% of full training data, reaching 97.25% of full-data training performance, demonstrating strong effectiveness in low-resource clinical settings. </t>
+  </si>
+  <si>
+    <t>GUSL: A Novel and Efficient Machine Learning Model for Prostate Segmentation on MRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prostate and zonal segmentation is a crucial step for clinical diagnosis of prostate cancer (PCa). Computer-aided diagnosis tools for prostate segmentation are based on the deep learning (DL) paradigm. However, deep neural networks are perceived as "black-box" solutions by physicians, thus making them less practical for deployment in the clinical setting. In this paper, we introduce a feed-forward machine learning model, named Green U-shaped Learning (GUSL), suitable for medical image segmentation without backpropagation. GUSL introduces a multi-layer regression scheme for coarse-to-fine segmentation. Its feature extraction is based on a linear model, which enables seamless interpretability during feature extraction. Also, GUSL introduces a mechanism for attention on the prostate boundaries, which is an error-prone region, by employing regression to refine the predictions through residue correction. In addition, a two-step pipeline approach is used to mitigate the class imbalance, an issue inherent in medical imaging problems. After conducting experiments on two publicly available datasets and one private dataset, in both prostate gland and zonal segmentation tasks, GUSL achieves state-of-the-art performance among other DL-based models. Notably, GUSL features a very energy-efficient pipeline, since it has a model size several times smaller and less complexity than the rest of the solutions. In all datasets, GUSL achieved a Dice Similarity Coefficient (DSC) performance greater than  for gland segmentation. Considering also its lightweight model size and transparency in feature extraction, it offers a competitive and practical package for medical imaging applications. </t>
+  </si>
+  <si>
+    <t>Diffusion Model-based Data Augmentation Method for Fetal Head Ultrasound Segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical image data is less accessible than in other domains due to privacy and regulatory constraints. In addition, labeling requires costly, time-intensive manual image annotation by clinical experts. To overcome these challenges, synthetic medical data generation offers a promising solution. Generative AI (GenAI), employing generative deep learning models, has proven effective at producing realistic synthetic images. This study proposes a novel mask-guided GenAI approach using diffusion models to generate synthetic fetal head ultrasound images paired with segmentation masks. These synthetic pairs augment real datasets for supervised fine-tuning of the Segment Anything Model (SAM). Our results show that the synthetic data captures real image features effectively, and this approach reaches state-of-the-art fetal head segmentation, especially when trained with a limited number of real image-mask pairs. In particular, the segmentation reaches Dice Scores of 94.66\% and 94.38\% using a handful of ultrasound images from the Spanish and African cohorts, respectively. Our code, models, and data are available on GitHub. </t>
+  </si>
+  <si>
+    <t>On the Domain Robustness of Contrastive Vision-Language Models</t>
+  </si>
+  <si>
+    <t>In real-world vision-language applications, practitioners increasingly rely on large, pretrained foundation models rather than custom-built solutions, despite limited transparency regarding their training data and processes. While these models achieve impressive performance on general benchmarks, their effectiveness can decline notably under specialized domain shifts, such as unique imaging conditions or environmental variations. In this work, we introduce Deepbench, a framework designed to assess domain-specific robustness of vision-language models (VLMs). Deepbench leverages a large language model (LLM) to generate realistic, context-aware image corruptions tailored to specific deployment domains without requiring labeled data. We evaluate a range of contrastive vision-language architectures and architectural variants across six real-world domains and observe substantial variability in robustness, highlighting the need for targeted, domain-aware evaluation. Deepbench is released as open-source software to support further research into domain-aware robustness assessment.</t>
+  </si>
+  <si>
+    <t>Brain Tumor Detection through Thermal Imaging and MobileNET</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Brain plays a crucial role in regulating body functions and cognitive processes, with brain tumors posing significant risks to human health. Precise and prompt detection is a key factor in proper treatment and better patient outcomes. Traditional methods for detecting brain tumors, that include biopsies, MRI, and CT scans often face challenges due to their high costs and the need for specialized medical expertise. Recent developments in machine learning (ML) and deep learning (DL) has exhibited strong capabilities in automating the identification and categorization of brain tumors from medical images, especially MRI scans. However, these classical ML models have limitations, such as high computational demands, the need for large datasets, and long training times, which hinder their accessibility and efficiency. Our research uses MobileNET model for efficient detection of these tumors. The novelty of this project lies in building an accurate tumor detection model which use less computing re-sources and runs in less time followed by efficient decision making through the use of image processing technique for accurate results. The suggested method attained an average accuracy of 98.5%. </t>
+  </si>
+  <si>
+    <t>TurboVSR: Fantastic Video Upscalers and Where to Find Them</t>
+  </si>
+  <si>
+    <t>iffusion-based generative models have demonstrated exceptional promise in the video super-resolution (VSR) task, achieving a substantial advancement in detail generation relative to prior methods. However, these approaches face significant computational efficiency challenges. For instance, current techniques may require tens of minutes to super-resolve a mere 2-second, 1080p video. In this paper, we present TurboVSR, an ultra-efficient diffusion-based video super-resolution model. Our core design comprises three key aspects: (1) We employ an autoencoder with a high compression ratio of 32328 to reduce the number of tokens. (2) Highly compressed latents pose substantial challenges for training. We introduce factorized conditioning to mitigate the learning complexity: we first learn to super-resolve the initial frame; subsequently, we condition the super-resolution of the remaining frames on the high-resolution initial frame and the low-resolution subsequent frames. (3) We convert the pre-trained diffusion model to a shortcut model to enable fewer sampling steps, further accelerating inference. As a result, TurboVSR performs on par with state-of-the-art VSR methods, while being 100+ times faster, taking only 7 seconds to process a 2-second long 1080p video. TurboVSR also supports image resolution by considering image as a one-frame video. Our efficient design makes SR beyond 1080p possible, results on 4K (36482048) image SR show surprising fine details</t>
+  </si>
+  <si>
+    <t>Transition Matching: Scalable and Flexible Generative Modeling</t>
+  </si>
+  <si>
+    <t>Diffusion and flow matching models have significantly advanced media generation, yet their design space is well-explored, somewhat limiting further improvements. Concurrently, autoregressive (AR) models, particularly those generating continuous tokens, have emerged as a promising direction for unifying text and media generation. This paper introduces Transition Matching (TM), a novel discrete-time, continuous-state generative paradigm that unifies and advances both diffusion/flow models and continuous AR generation. TM decomposes complex generation tasks into simpler Markov transitions, allowing for expressive non-deterministic probability transition kernels and arbitrary non-continuous supervision processes, thereby unlocking new flexible design avenues. We explore these choices through three TM variants: (i) Difference Transition Matching (DTM), which generalizes flow matching to discrete-time by directly learning transition probabilities, yielding state-of-the-art image quality and text adherence as well as improved sampling efficiency. (ii) Autoregressive Transition Matching (ARTM) and (iii) Full History Transition Matching (FHTM) are partially and fully causal models, respectively, that generalize continuous AR methods. They achieve continuous causal AR generation quality comparable to non-causal approaches and potentially enable seamless integration with existing AR text generation techniques. Notably, FHTM is the first fully causal model to match or surpass the performance of flow-based methods on text-to-image task in continuous domains. We demonstrate these contributions through a rigorous large-scale comparison of TM variants and relevant baselines, maintaining a fixed architecture, training data, and hyperparameters.</t>
+  </si>
+  <si>
+    <t>A Clinically-Grounded Two-Stage Framework for Renal CT Report Generation</t>
+  </si>
+  <si>
+    <t>Generating radiology reports from CT scans remains a complex task due to the nuanced nature of medical imaging and the variability in clinical documentation. In this study, we propose a two-stage framework for generating renal radiology reports from 2D CT slices. First, we extract structured abnormality features using a multi-task learning model trained to identify lesion attributes such as location, size, enhancement, and attenuation. These extracted features are subsequently combined with the corresponding CT image and fed into a fine-tuned vision-language model to generate natural language report sentences aligned with clinical findings. We conduct experiments on a curated dataset of renal CT studies with manually annotated sentence-slice-feature triplets and evaluate performance using both classification metrics and natural language generation metrics. Our results demonstrate that the proposed model outperforms random baselines across all abnormality types, and the generated reports capture key clinical content with reasonable textual accuracy. This exploratory work highlights the feasibility of modular, feature-informed report generation for renal imaging. Future efforts will focus on extending this pipeline to 3D CT volumes and further improving clinical fidelity in multimodal medical AI systems.</t>
+  </si>
+  <si>
+    <t>A Fast and Accurate 3-D Reconstruction Algorithm for Near-Range Microwave Imaging with Handheld Synthetic Aperture Radar</t>
+  </si>
+  <si>
+    <t>The design of image reconstruction algorithms for near-range handheld synthetic aperture radar (SAR) systems has gained increasing popularity due to the promising performance of portable millimeter-wave (MMW) imaging devices in various application fields. Time domain imaging algorithms including the backprojection algorithm (BPA) and the Kirchhoff migration algorithm (KMA) are widely adopted due to their direct applicability to arbitrary scan trajectories. However, they suffer from time complexity issues that hinder their practical application. Wavenumber domain algorithms greatly improve the computational efficiency but most of them are restricted to specific array topologies. Based on the factorization techniques as adopted in far-field synthetic aperture radar imaging, the time domain fast factorized backprojection algorithm for handheld synthetic aperture radar (HHFFBPA) is proposed. The local spectral properties of the radar images for handheld systems are analyzed and analytical spectrum compression techniques are derived to realize efficient sampling of the subimages. Validated through numerical simulations and experiments, HHFFBPA achieves fast and accurate 3-D imaging for handheld synthetic aperture radar systems with arbitrary trajectories.</t>
+  </si>
+  <si>
+    <t>Metadata, Wavelet, and Time Aware Diffusion Models for Satellite Image Super Resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The acquisition of high-resolution satellite imagery is often constrained by the spatial and temporal limitations of satellite sensors, as well as the high costs associated with frequent observations. These challenges hinder applications such as environmental monitoring, disaster response, and agricultural management, which require fine-grained and high-resolution data. In this paper, we propose MWT-Diff, an innovative framework for satellite image super-resolution (SR) that combines latent diffusion models with wavelet transforms to address these challenges. At the core of the framework is a novel metadata-, wavelet-, and time-aware encoder (MWT-Encoder), which generates embeddings that capture metadata attributes, multi-scale frequency information, and temporal relationships. The embedded feature representations steer the hierarchical diffusion dynamics, through which the model progressively reconstructs high-resolution satellite imagery from low-resolution inputs. This process preserves critical spatial characteristics including textural patterns, boundary discontinuities, and high-frequency spectral components essential for detailed remote sensing analysis. The comparative analysis of MWT-Diff across multiple datasets demonstrated favorable performance compared to recent approaches, as measured by standard perceptual quality metrics including FID and LPIPS.</t>
+  </si>
+  <si>
+    <t>Oneta: Multi-Style Image Enhancement Using Eigentransformation Functions</t>
+  </si>
+  <si>
+    <t>The first algorithm, called Oneta, for a novel task of multi-style image enhancement is proposed in this work. Oneta uses two point operators sequentially: intensity enhancement with a transformation function (TF) and color correction with a color correction matrix (CCM). This two-step enhancement model, though simple, achieves a high performance upper bound. Also, we introduce eigentransformation function (eigenTF) to represent TF compactly. The Oneta network comprises Y-Net and C-Net to predict eigenTF and CCM parameters, respectively. To support  styles, Oneta employs  learnable tokens. During training, each style token is learned using image pairs from the corresponding dataset. In testing, Oneta selects one of the  style tokens to enhance an image accordingly. Extensive experiments show that the single Oneta network can effectively undertake six enhancement tasks -- retouching, image signal processing, low-light image enhancement, dehazing, underwater image enhancement, and white balancing -- across 30 datasets.</t>
+  </si>
+  <si>
+    <t>Pyramidal Patchification Flow for Visual Generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Diffusion transformers (DiTs) adopt Patchify, mapping patch representations to token representations through linear projections, to adjust the number of tokens input to DiT blocks and thus the computation cost. Instead of a single patch size for all the timesteps, we introduce a Pyramidal Patchification Flow (PPFlow) approach: Large patch sizes are used for high noise timesteps and small patch sizes for low noise timesteps; Linear projections are learned for each patch size; and Unpatchify is accordingly modified. Unlike Pyramidal Flow, our approach operates over full latent representations other than pyramid representations, and adopts the normal denoising process without requiring the renoising trick. We demonstrate the effectiveness of our approach through two training manners. Training from scratch achieves a  () inference speed over SiT-B/2 for 2-level (3-level) pyramid patchification with slightly lower training FLOPs and similar image generation performance. Training from pretrained normal DiTs achieves even better performance with small training time. The code and checkpoint are at https://github.com/fudan-generative-vision/PPFlow.</t>
+  </si>
+  <si>
+    <t>Consistent Time-of-Flight Depth Denoising via Graph-Informed Geometric Attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depth images captured by Time-of-Flight (ToF) sensors are prone to noise, requiring denoising for reliable downstream applications. Previous works either focus on single-frame processing, or perform multi-frame processing without considering depth variations at corresponding pixels across frames, leading to undesirable temporal inconsistency and spatial ambiguity. In this paper, we propose a novel ToF depth denoising network leveraging motion-invariant graph fusion to simultaneously enhance temporal stability and spatial sharpness. Specifically, despite depth shifts across frames, graph structures exhibit temporal self-similarity, enabling cross-frame geometric attention for graph fusion. Then, by incorporating an image smoothness prior on the fused graph and data fidelity term derived from ToF noise distribution, we formulate a maximum a posterior problem for ToF denoising. Finally, the solution is unrolled into iterative filters whose weights are adaptively learned from the graph-informed geometric attention, producing a high-performance yet interpretable network. Experimental results demonstrate that the proposed scheme achieves state-of-the-art performance in terms of accuracy and consistency on synthetic DVToF dataset and exhibits robust generalization on the real Kinectv2 dataset. Source code will be released at \href{https://github.com/davidweidawang/GIGA-ToF}{https://github.com/davidweidawang/GIGA-ToF}. </t>
   </si>
 </sst>
 </file>
@@ -1854,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8EA504-630C-49F1-ADFD-D2E2B7A56A3C}">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4877,6 +5790,2109 @@
         <v>323</v>
       </c>
       <c r="F151" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>479</v>
+      </c>
+      <c r="C152" t="s">
+        <v>480</v>
+      </c>
+      <c r="F152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>481</v>
+      </c>
+      <c r="C153" t="s">
+        <v>482</v>
+      </c>
+      <c r="F153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>483</v>
+      </c>
+      <c r="C154" t="s">
+        <v>484</v>
+      </c>
+      <c r="F154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>485</v>
+      </c>
+      <c r="C155" t="s">
+        <v>486</v>
+      </c>
+      <c r="F155" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>487</v>
+      </c>
+      <c r="C156" t="s">
+        <v>488</v>
+      </c>
+      <c r="F156" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>489</v>
+      </c>
+      <c r="C157" t="s">
+        <v>490</v>
+      </c>
+      <c r="F157" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>491</v>
+      </c>
+      <c r="C158" t="s">
+        <v>492</v>
+      </c>
+      <c r="F158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>493</v>
+      </c>
+      <c r="C159" t="s">
+        <v>494</v>
+      </c>
+      <c r="F159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>495</v>
+      </c>
+      <c r="C160" t="s">
+        <v>496</v>
+      </c>
+      <c r="F160" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>497</v>
+      </c>
+      <c r="C161" t="s">
+        <v>498</v>
+      </c>
+      <c r="F161" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>499</v>
+      </c>
+      <c r="C162" t="s">
+        <v>500</v>
+      </c>
+      <c r="F162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>501</v>
+      </c>
+      <c r="C163" t="s">
+        <v>502</v>
+      </c>
+      <c r="F163" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>503</v>
+      </c>
+      <c r="C164" t="s">
+        <v>504</v>
+      </c>
+      <c r="F164" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>506</v>
+      </c>
+      <c r="C165" t="s">
+        <v>505</v>
+      </c>
+      <c r="F165" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>507</v>
+      </c>
+      <c r="C166" t="s">
+        <v>508</v>
+      </c>
+      <c r="F166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>509</v>
+      </c>
+      <c r="C167" t="s">
+        <v>510</v>
+      </c>
+      <c r="F167" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>511</v>
+      </c>
+      <c r="C168" t="s">
+        <v>512</v>
+      </c>
+      <c r="F168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>513</v>
+      </c>
+      <c r="C169" t="s">
+        <v>514</v>
+      </c>
+      <c r="F169" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>515</v>
+      </c>
+      <c r="C170" t="s">
+        <v>516</v>
+      </c>
+      <c r="F170" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>517</v>
+      </c>
+      <c r="C171" t="s">
+        <v>518</v>
+      </c>
+      <c r="F171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>519</v>
+      </c>
+      <c r="C172" t="s">
+        <v>520</v>
+      </c>
+      <c r="F172" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>521</v>
+      </c>
+      <c r="C173" t="s">
+        <v>522</v>
+      </c>
+      <c r="F173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>523</v>
+      </c>
+      <c r="C174" t="s">
+        <v>524</v>
+      </c>
+      <c r="F174" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>525</v>
+      </c>
+      <c r="C175" t="s">
+        <v>526</v>
+      </c>
+      <c r="F175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>527</v>
+      </c>
+      <c r="C176" t="s">
+        <v>528</v>
+      </c>
+      <c r="F176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>529</v>
+      </c>
+      <c r="C177" t="s">
+        <v>530</v>
+      </c>
+      <c r="F177" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>531</v>
+      </c>
+      <c r="C178" t="s">
+        <v>532</v>
+      </c>
+      <c r="F178" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>533</v>
+      </c>
+      <c r="C179" t="s">
+        <v>534</v>
+      </c>
+      <c r="F179" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>535</v>
+      </c>
+      <c r="C180" t="s">
+        <v>536</v>
+      </c>
+      <c r="F180" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>537</v>
+      </c>
+      <c r="C181" t="s">
+        <v>538</v>
+      </c>
+      <c r="F181" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>539</v>
+      </c>
+      <c r="C182" t="s">
+        <v>540</v>
+      </c>
+      <c r="F182" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>541</v>
+      </c>
+      <c r="C183" t="s">
+        <v>542</v>
+      </c>
+      <c r="F183" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>543</v>
+      </c>
+      <c r="C184" t="s">
+        <v>544</v>
+      </c>
+      <c r="F184" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>545</v>
+      </c>
+      <c r="C185" t="s">
+        <v>546</v>
+      </c>
+      <c r="F185" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>547</v>
+      </c>
+      <c r="C186" t="s">
+        <v>548</v>
+      </c>
+      <c r="F186" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>549</v>
+      </c>
+      <c r="C187" t="s">
+        <v>550</v>
+      </c>
+      <c r="F187" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>551</v>
+      </c>
+      <c r="C188" t="s">
+        <v>552</v>
+      </c>
+      <c r="F188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>553</v>
+      </c>
+      <c r="C189" t="s">
+        <v>554</v>
+      </c>
+      <c r="F189" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>555</v>
+      </c>
+      <c r="C190" t="s">
+        <v>556</v>
+      </c>
+      <c r="F190" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>557</v>
+      </c>
+      <c r="C191" t="s">
+        <v>558</v>
+      </c>
+      <c r="F191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>559</v>
+      </c>
+      <c r="C192" t="s">
+        <v>560</v>
+      </c>
+      <c r="F192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>561</v>
+      </c>
+      <c r="C193" t="s">
+        <v>562</v>
+      </c>
+      <c r="F193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>563</v>
+      </c>
+      <c r="C194" t="s">
+        <v>564</v>
+      </c>
+      <c r="F194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>565</v>
+      </c>
+      <c r="C195" t="s">
+        <v>566</v>
+      </c>
+      <c r="F195" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>567</v>
+      </c>
+      <c r="C196" t="s">
+        <v>568</v>
+      </c>
+      <c r="F196" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>569</v>
+      </c>
+      <c r="C197" t="s">
+        <v>570</v>
+      </c>
+      <c r="F197" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>571</v>
+      </c>
+      <c r="C198" t="s">
+        <v>572</v>
+      </c>
+      <c r="F198" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>573</v>
+      </c>
+      <c r="C199" t="s">
+        <v>574</v>
+      </c>
+      <c r="F199" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>575</v>
+      </c>
+      <c r="C200" t="s">
+        <v>576</v>
+      </c>
+      <c r="F200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>577</v>
+      </c>
+      <c r="C201" t="s">
+        <v>578</v>
+      </c>
+      <c r="F201" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>579</v>
+      </c>
+      <c r="C202" t="s">
+        <v>580</v>
+      </c>
+      <c r="F202" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>579</v>
+      </c>
+      <c r="C203" t="s">
+        <v>580</v>
+      </c>
+      <c r="F203" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>581</v>
+      </c>
+      <c r="C204" t="s">
+        <v>582</v>
+      </c>
+      <c r="F204" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>583</v>
+      </c>
+      <c r="C205" t="s">
+        <v>584</v>
+      </c>
+      <c r="F205" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>585</v>
+      </c>
+      <c r="C206" t="s">
+        <v>586</v>
+      </c>
+      <c r="F206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>587</v>
+      </c>
+      <c r="C207" t="s">
+        <v>588</v>
+      </c>
+      <c r="F207" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>589</v>
+      </c>
+      <c r="C208" t="s">
+        <v>590</v>
+      </c>
+      <c r="F208" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>591</v>
+      </c>
+      <c r="C209" t="s">
+        <v>592</v>
+      </c>
+      <c r="F209" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>593</v>
+      </c>
+      <c r="C210" t="s">
+        <v>594</v>
+      </c>
+      <c r="F210" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>595</v>
+      </c>
+      <c r="C211" t="s">
+        <v>596</v>
+      </c>
+      <c r="F211" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>597</v>
+      </c>
+      <c r="C212" t="s">
+        <v>598</v>
+      </c>
+      <c r="F212" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>599</v>
+      </c>
+      <c r="C213" t="s">
+        <v>600</v>
+      </c>
+      <c r="F213" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>601</v>
+      </c>
+      <c r="C214" t="s">
+        <v>602</v>
+      </c>
+      <c r="F214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>603</v>
+      </c>
+      <c r="C215" t="s">
+        <v>604</v>
+      </c>
+      <c r="F215" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>605</v>
+      </c>
+      <c r="C216" t="s">
+        <v>606</v>
+      </c>
+      <c r="F216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>607</v>
+      </c>
+      <c r="C217" t="s">
+        <v>608</v>
+      </c>
+      <c r="F217" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>609</v>
+      </c>
+      <c r="C218" t="s">
+        <v>610</v>
+      </c>
+      <c r="F218" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>611</v>
+      </c>
+      <c r="C219" t="s">
+        <v>612</v>
+      </c>
+      <c r="F219" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>613</v>
+      </c>
+      <c r="C220" t="s">
+        <v>614</v>
+      </c>
+      <c r="F220" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>615</v>
+      </c>
+      <c r="C221" t="s">
+        <v>616</v>
+      </c>
+      <c r="F221" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>617</v>
+      </c>
+      <c r="C222" t="s">
+        <v>618</v>
+      </c>
+      <c r="F222" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>619</v>
+      </c>
+      <c r="C223" t="s">
+        <v>620</v>
+      </c>
+      <c r="F223" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>621</v>
+      </c>
+      <c r="C224" t="s">
+        <v>622</v>
+      </c>
+      <c r="F224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>622</v>
+      </c>
+      <c r="C225" t="s">
+        <v>623</v>
+      </c>
+      <c r="F225" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>624</v>
+      </c>
+      <c r="C226" t="s">
+        <v>625</v>
+      </c>
+      <c r="F226" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>626</v>
+      </c>
+      <c r="C227" t="s">
+        <v>627</v>
+      </c>
+      <c r="F227" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>628</v>
+      </c>
+      <c r="C228" t="s">
+        <v>629</v>
+      </c>
+      <c r="F228" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>630</v>
+      </c>
+      <c r="C229" t="s">
+        <v>631</v>
+      </c>
+      <c r="F229" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>632</v>
+      </c>
+      <c r="C230" t="s">
+        <v>633</v>
+      </c>
+      <c r="F230" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>634</v>
+      </c>
+      <c r="C231" t="s">
+        <v>635</v>
+      </c>
+      <c r="F231" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>636</v>
+      </c>
+      <c r="C232" t="s">
+        <v>637</v>
+      </c>
+      <c r="F232" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>638</v>
+      </c>
+      <c r="C233" t="s">
+        <v>639</v>
+      </c>
+      <c r="F233" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>640</v>
+      </c>
+      <c r="C234" t="s">
+        <v>641</v>
+      </c>
+      <c r="F234" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>642</v>
+      </c>
+      <c r="C235" t="s">
+        <v>643</v>
+      </c>
+      <c r="F235" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>644</v>
+      </c>
+      <c r="C236" t="s">
+        <v>645</v>
+      </c>
+      <c r="F236" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>646</v>
+      </c>
+      <c r="C237" t="s">
+        <v>647</v>
+      </c>
+      <c r="F237" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>648</v>
+      </c>
+      <c r="C238" t="s">
+        <v>649</v>
+      </c>
+      <c r="F238" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>650</v>
+      </c>
+      <c r="C239" t="s">
+        <v>651</v>
+      </c>
+      <c r="F239" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>652</v>
+      </c>
+      <c r="C240" t="s">
+        <v>653</v>
+      </c>
+      <c r="F240" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>654</v>
+      </c>
+      <c r="C241" t="s">
+        <v>655</v>
+      </c>
+      <c r="F241" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>656</v>
+      </c>
+      <c r="C242" t="s">
+        <v>657</v>
+      </c>
+      <c r="F242" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>658</v>
+      </c>
+      <c r="C243" t="s">
+        <v>659</v>
+      </c>
+      <c r="F243" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>660</v>
+      </c>
+      <c r="C244" t="s">
+        <v>661</v>
+      </c>
+      <c r="F244" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>662</v>
+      </c>
+      <c r="C245" t="s">
+        <v>663</v>
+      </c>
+      <c r="F245" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>664</v>
+      </c>
+      <c r="C246" t="s">
+        <v>665</v>
+      </c>
+      <c r="F246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>666</v>
+      </c>
+      <c r="C247" t="s">
+        <v>667</v>
+      </c>
+      <c r="F247" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>668</v>
+      </c>
+      <c r="C248" t="s">
+        <v>669</v>
+      </c>
+      <c r="F248" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>670</v>
+      </c>
+      <c r="C249" t="s">
+        <v>671</v>
+      </c>
+      <c r="F249" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>672</v>
+      </c>
+      <c r="C250" t="s">
+        <v>673</v>
+      </c>
+      <c r="F250" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>674</v>
+      </c>
+      <c r="C251" t="s">
+        <v>675</v>
+      </c>
+      <c r="F251" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>676</v>
+      </c>
+      <c r="C252" t="s">
+        <v>677</v>
+      </c>
+      <c r="F252" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>678</v>
+      </c>
+      <c r="C253" t="s">
+        <v>679</v>
+      </c>
+      <c r="F253" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>680</v>
+      </c>
+      <c r="C254" t="s">
+        <v>681</v>
+      </c>
+      <c r="F254" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>682</v>
+      </c>
+      <c r="C255" t="s">
+        <v>683</v>
+      </c>
+      <c r="F255" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>684</v>
+      </c>
+      <c r="C256" t="s">
+        <v>685</v>
+      </c>
+      <c r="F256" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>686</v>
+      </c>
+      <c r="C257" t="s">
+        <v>687</v>
+      </c>
+      <c r="F257" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>688</v>
+      </c>
+      <c r="C258" t="s">
+        <v>689</v>
+      </c>
+      <c r="F258" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>690</v>
+      </c>
+      <c r="C259" t="s">
+        <v>691</v>
+      </c>
+      <c r="F259" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>692</v>
+      </c>
+      <c r="C260" t="s">
+        <v>693</v>
+      </c>
+      <c r="F260" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>694</v>
+      </c>
+      <c r="C261" t="s">
+        <v>695</v>
+      </c>
+      <c r="F261" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>696</v>
+      </c>
+      <c r="C262" t="s">
+        <v>697</v>
+      </c>
+      <c r="F262" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>698</v>
+      </c>
+      <c r="C263" t="s">
+        <v>699</v>
+      </c>
+      <c r="F263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>700</v>
+      </c>
+      <c r="C264" t="s">
+        <v>701</v>
+      </c>
+      <c r="F264" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>702</v>
+      </c>
+      <c r="C265" t="s">
+        <v>703</v>
+      </c>
+      <c r="F265" t="s">
+        <v>6</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>705</v>
+      </c>
+      <c r="C266" t="s">
+        <v>706</v>
+      </c>
+      <c r="F266" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>707</v>
+      </c>
+      <c r="C267" t="s">
+        <v>708</v>
+      </c>
+      <c r="F267" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>709</v>
+      </c>
+      <c r="C268" t="s">
+        <v>710</v>
+      </c>
+      <c r="F268" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>711</v>
+      </c>
+      <c r="C269" t="s">
+        <v>712</v>
+      </c>
+      <c r="F269" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>713</v>
+      </c>
+      <c r="C270" t="s">
+        <v>714</v>
+      </c>
+      <c r="F270" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>715</v>
+      </c>
+      <c r="C271" t="s">
+        <v>716</v>
+      </c>
+      <c r="F271" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>717</v>
+      </c>
+      <c r="C272" t="s">
+        <v>718</v>
+      </c>
+      <c r="F272" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>719</v>
+      </c>
+      <c r="C273" t="s">
+        <v>720</v>
+      </c>
+      <c r="F273" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>721</v>
+      </c>
+      <c r="C274" t="s">
+        <v>722</v>
+      </c>
+      <c r="F274" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>723</v>
+      </c>
+      <c r="C275" t="s">
+        <v>724</v>
+      </c>
+      <c r="F275" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>725</v>
+      </c>
+      <c r="C276" t="s">
+        <v>726</v>
+      </c>
+      <c r="F276" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>727</v>
+      </c>
+      <c r="C277" t="s">
+        <v>728</v>
+      </c>
+      <c r="F277" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>729</v>
+      </c>
+      <c r="C278" t="s">
+        <v>730</v>
+      </c>
+      <c r="F278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>731</v>
+      </c>
+      <c r="C279" t="s">
+        <v>732</v>
+      </c>
+      <c r="F279" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>733</v>
+      </c>
+      <c r="C280" t="s">
+        <v>734</v>
+      </c>
+      <c r="F280" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>735</v>
+      </c>
+      <c r="C281" t="s">
+        <v>736</v>
+      </c>
+      <c r="F281" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>737</v>
+      </c>
+      <c r="C282" t="s">
+        <v>738</v>
+      </c>
+      <c r="F282" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>739</v>
+      </c>
+      <c r="C283" t="s">
+        <v>740</v>
+      </c>
+      <c r="F283" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>741</v>
+      </c>
+      <c r="C284" t="s">
+        <v>742</v>
+      </c>
+      <c r="F284" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>743</v>
+      </c>
+      <c r="C285" t="s">
+        <v>744</v>
+      </c>
+      <c r="F285" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>745</v>
+      </c>
+      <c r="C286" t="s">
+        <v>746</v>
+      </c>
+      <c r="F286" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>747</v>
+      </c>
+      <c r="C287" t="s">
+        <v>748</v>
+      </c>
+      <c r="F287" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>749</v>
+      </c>
+      <c r="C288" t="s">
+        <v>750</v>
+      </c>
+      <c r="F288" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>751</v>
+      </c>
+      <c r="C289" t="s">
+        <v>752</v>
+      </c>
+      <c r="F289" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>753</v>
+      </c>
+      <c r="C290" t="s">
+        <v>754</v>
+      </c>
+      <c r="F290" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>755</v>
+      </c>
+      <c r="C291" t="s">
+        <v>756</v>
+      </c>
+      <c r="F291" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>757</v>
+      </c>
+      <c r="C292" t="s">
+        <v>758</v>
+      </c>
+      <c r="F292" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>759</v>
+      </c>
+      <c r="C293" t="s">
+        <v>760</v>
+      </c>
+      <c r="F293" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>761</v>
+      </c>
+      <c r="C294" t="s">
+        <v>762</v>
+      </c>
+      <c r="F294" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>763</v>
+      </c>
+      <c r="C295" t="s">
+        <v>764</v>
+      </c>
+      <c r="F295" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>765</v>
+      </c>
+      <c r="C296" t="s">
+        <v>766</v>
+      </c>
+      <c r="F296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>767</v>
+      </c>
+      <c r="C297" t="s">
+        <v>768</v>
+      </c>
+      <c r="F297" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>769</v>
+      </c>
+      <c r="C298" t="s">
+        <v>770</v>
+      </c>
+      <c r="F298" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>771</v>
+      </c>
+      <c r="C299" t="s">
+        <v>772</v>
+      </c>
+      <c r="F299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>773</v>
+      </c>
+      <c r="C300" t="s">
+        <v>774</v>
+      </c>
+      <c r="F300" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>775</v>
+      </c>
+      <c r="C301" t="s">
+        <v>776</v>
+      </c>
+      <c r="F301" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5032,8 +8048,9 @@
     <hyperlink ref="E149" r:id="rId148" xr:uid="{DEB52587-2DE5-4E25-9CE8-51F5F123DBBA}"/>
     <hyperlink ref="E150" r:id="rId149" xr:uid="{561BE496-0CDA-4A82-BEB3-2AF871261DCC}"/>
     <hyperlink ref="E151" r:id="rId150" xr:uid="{640AD9C7-8847-4867-82CA-0AF686C2928E}"/>
+    <hyperlink ref="G265" r:id="rId151" xr:uid="{691A4ACC-EF28-49E1-A820-B82653720CF8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId151"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId152"/>
 </worksheet>
 </file>